--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0 &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -124,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,10 +148,22 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +179,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -524,14 +550,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Une ligne = une annonce. Coche la colonne « Fait » au fur et à mesure.</t>
+          <t>Une ligne = une annonce. La colonne URSSAF est le montant à provisionner dès l'encaissement.</t>
         </is>
       </c>
     </row>
@@ -561,15 +589,25 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>URSSAF 12,4 %</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Reste après URSSAF</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>Où le vendre</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Fait</t>
         </is>
@@ -585,6 +623,8 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -595,34 +635,50 @@
       <c r="B6" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8">
+        <f>B6*0.124</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Texte d'annonce prêt · plancher 129 €</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n"/>
+      <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="14">
+        <f>B7*0.124</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -633,38 +689,54 @@
       <c r="B8" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8">
+        <f>B8*0.124</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Vérifier marquage CE et notice FR</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n"/>
+      <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="14">
+        <f>B9*0.124</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Vérifier marquage CE et notice FR</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -675,49 +747,67 @@
       <c r="B10" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8">
+        <f>B10*0.124</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n"/>
+      <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="14">
+        <f>B11*0.124</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n"/>
+      <c r="G11" s="17" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -728,38 +818,54 @@
       <c r="B13" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8">
+        <f>B13*0.124</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Boutique + Vinted + Leboncoin</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>À recevoir</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n"/>
+      <c r="G13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>BMW Overall ProRain unisexe noir — XL</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="13" t="n">
         <v>139</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="14">
+        <f>B14*0.124</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>À recevoir</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n"/>
+      <c r="G14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -770,38 +876,54 @@
       <c r="B15" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8">
+        <f>B15*0.124</f>
+        <v/>
+      </c>
+      <c r="D15" s="9">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Saison rando : sept-nov</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n"/>
+      <c r="G15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="13" t="n">
         <v>99</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="14">
+        <f>B16*0.124</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Défroisser avant photos</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n"/>
+      <c r="G16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -812,38 +934,54 @@
       <c r="B17" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8">
+        <f>B17*0.124</f>
+        <v/>
+      </c>
+      <c r="D17" s="9">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Vérifier composition sur l'étiquette</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n"/>
+      <c r="G17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="14">
+        <f>B18*0.124</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Indiquer les deux tailles</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
+      <c r="G18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -854,38 +992,54 @@
       <c r="B19" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8">
+        <f>B19*0.124</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n"/>
+      <c r="G19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Adidas Predator Edge.1 TF — 48⅔ — 2ᵉ paire</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="14">
+        <f>B20*0.124</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n"/>
+      <c r="G20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -896,38 +1050,54 @@
       <c r="B21" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8">
+        <f>B21*0.124</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Retirer de Vinted d'abord</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n"/>
+      <c r="G21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Plein Sport montante blanc / violet — 40</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="14">
+        <f>B22*0.124</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>99 € pendant 2 semaines, puis 89 €</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n"/>
+      <c r="G22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -938,30 +1108,46 @@
       <c r="B23" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8">
+        <f>B23*0.124</f>
+        <v/>
+      </c>
+      <c r="D23" s="9">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Baskets adidas by Stella McCartney UB21 — 36</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="13" t="n">
         <v>79</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="14">
+        <f>B24*0.124</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -972,34 +1158,50 @@
       <c r="B25" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8">
+        <f>B25*0.124</f>
+        <v/>
+      </c>
+      <c r="D25" s="9">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="11" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="13" t="n">
         <v>59</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="14">
+        <f>B26*0.124</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Pas Vinted : article neuf</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n"/>
+      <c r="G26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1010,34 +1212,50 @@
       <c r="B27" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8">
+        <f>B27*0.124</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Orthographe : Pier ANTONIO</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n"/>
+      <c r="G27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Baskets Geox gris / argent — 35</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="14">
+        <f>B28*0.124</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1048,30 +1266,46 @@
       <c r="B29" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="8">
+        <f>B29*0.124</f>
+        <v/>
+      </c>
+      <c r="D29" s="9">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="11" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Morgan — jupe marron</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="14">
+        <f>B30*0.124</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1082,30 +1316,46 @@
       <c r="B31" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="8">
+        <f>B31*0.124</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Morgan — polo rouge à écusson doré L</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="14">
+        <f>B32*0.124</f>
+        <v/>
+      </c>
+      <c r="D32" s="15">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="16" t="inlineStr"/>
+      <c r="G32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1116,41 +1366,59 @@
       <c r="B33" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="8">
+        <f>B33*0.124</f>
+        <v/>
+      </c>
+      <c r="D33" s="9">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="11" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Morgan — polo blanc L</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="14">
+        <f>B34*0.124</f>
+        <v/>
+      </c>
+      <c r="D34" s="15">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="16" t="inlineStr"/>
+      <c r="G34" s="17" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1161,34 +1429,50 @@
       <c r="B36" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="8">
+        <f>B36*0.124</f>
+        <v/>
+      </c>
+      <c r="D36" s="9">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Préciser « modèle GS », réf. G19064IK</t>
         </is>
       </c>
-      <c r="E36" s="9" t="n"/>
+      <c r="G36" s="11" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="14">
+        <f>B37*0.124</f>
+        <v/>
+      </c>
+      <c r="D37" s="15">
+        <f>B37-C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="16" t="inlineStr"/>
+      <c r="G37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1199,30 +1483,46 @@
       <c r="B38" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="8">
+        <f>B38*0.124</f>
+        <v/>
+      </c>
+      <c r="D38" s="9">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="11" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante — 44</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="14">
+        <f>B39*0.124</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>B39-C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr"/>
-      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="16" t="inlineStr"/>
+      <c r="G39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1233,24 +1533,34 @@
       <c r="B40" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="8">
+        <f>B40*0.124</f>
+        <v/>
+      </c>
+      <c r="D40" s="9">
+        <f>B40-C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="11" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="19" t="n"/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1261,54 +1571,80 @@
       <c r="B42" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="8">
+        <f>B42*0.124</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="E42" s="9" t="n"/>
+      <c r="G42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
         </is>
       </c>
-      <c r="E43" s="13" t="n"/>
+      <c r="G43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>TOTAL — 34 annonces</t>
-        </is>
-      </c>
-      <c r="B44" s="22">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL — 34 annonces chiffrées</t>
+        </is>
+      </c>
+      <c r="B44" s="26">
         <f>B6+B7+B8+B9+B10+B11+B13+B14+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B36+B37+B38+B39+B40+B42</f>
         <v/>
       </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
+      <c r="C44" s="27">
+        <f>B44*0.124</f>
+        <v/>
+      </c>
+      <c r="D44" s="26">
+        <f>B44-C44</f>
+        <v/>
+      </c>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1321,6 +1657,13 @@
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -71,7 +71,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8449"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,35 +161,37 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -616,7 +623,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
+          <t>✅ VENDU</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -629,11 +636,11 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Havaianas Slim fuchsia 35/36 — LOT de 10 paires</t>
+          <t>Salomon X Ultra 5 Mid GTX — 44</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C6" s="8">
         <f>B6*0.124</f>
@@ -645,49 +652,37 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Texte d'annonce prêt · plancher 129 €</t>
+          <t>Vendue le 12/08 · expédier avant le 19/08 20h12</t>
         </is>
       </c>
       <c r="G6" s="11" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="C7" s="14">
-        <f>B7*0.124</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Boutique + Leboncoin</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="n"/>
+          <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
+          <t>Havaianas Slim fuchsia 35/36 — LOT de 10 paires</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="C8" s="8">
         <f>B8*0.124</f>
@@ -699,49 +694,45 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Vérifier marquage CE et notice FR</t>
+          <t>Texte d'annonce prêt · plancher 129 €</t>
         </is>
       </c>
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" s="16">
         <f>B9*0.124</f>
         <v/>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="17">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>Vérifier marquage CE et notice FR</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="n"/>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -762,119 +753,119 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
+          <t>Vérifier marquage CE et notice FR</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="C11" s="16">
+        <f>B11*0.124</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Vérifier marquage CE et notice FR</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C12" s="8">
+        <f>B12*0.124</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
           <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="G12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B13" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C11" s="14">
-        <f>B11*0.124</f>
-        <v/>
-      </c>
-      <c r="D11" s="15">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C13" s="16">
+        <f>B13*0.124</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
-      <c r="G11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="G13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Bottes Forma Legacy Waterproof — 45</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="C13" s="8">
-        <f>B13*0.124</f>
-        <v/>
-      </c>
-      <c r="D13" s="9">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Boutique + Vinted + Leboncoin</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>À recevoir</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>BMW Overall ProRain unisexe noir — XL</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>139</v>
-      </c>
-      <c r="C14" s="14">
-        <f>B14*0.124</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>À recevoir</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Salomon X Ultra 5 Mid GTX — 44</t>
+          <t>Bottes Forma Legacy Waterproof — 45</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="C15" s="8">
         <f>B15*0.124</f>
@@ -886,49 +877,49 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique + Vinted + Leboncoin</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Saison rando : sept-nov</t>
+          <t>À recevoir</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>99</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>BMW Overall ProRain unisexe noir — XL</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="C16" s="16">
         <f>B16*0.124</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>Défroisser avant photos</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="n"/>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>À recevoir</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
+          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -949,44 +940,44 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
+          <t>Défroisser avant photos</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C18" s="16">
+        <f>B18*0.124</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
           <t>Vérifier composition sur l'étiquette</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="C18" s="14">
-        <f>B18*0.124</f>
-        <v/>
-      </c>
-      <c r="D18" s="15">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Indiquer les deux tailles</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="n"/>
+      <c r="G18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
+          <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -1002,49 +993,49 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Indiquer les deux tailles</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="C20" s="16">
+        <f>B20*0.124</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Adidas Predator Edge.1 TF — 48⅔ — 2ᵉ paire</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="C20" s="14">
-        <f>B20*0.124</f>
-        <v/>
-      </c>
-      <c r="D20" s="15">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>eBay + Leboncoin</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>Une annonce par paire</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Robe Sandro Noaim blanche — 40</t>
+          <t>Adidas Predator Edge.1 TF — 48⅔ — 2ᵉ paire</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
@@ -1060,53 +1051,53 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>eBay + Leboncoin</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Une annonce par paire</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Robe Sandro Noaim blanche — 40</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="C22" s="16">
+        <f>B22*0.124</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>Retirer de Vinted d'abord</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Plein Sport montante blanc / violet — 40</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="C22" s="14">
-        <f>B22*0.124</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>99 € pendant 2 semaines, puis 89 €</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="n"/>
+      <c r="G22" s="19" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Ballerines Hogan 186 Zeppa Fashion — 36</t>
+          <t>Plein Sport montante blanc / violet — 40</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C23" s="8">
         <f>B23*0.124</f>
@@ -1118,45 +1109,49 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>99 € pendant 2 semaines, puis 89 €</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Ballerines Hogan 186 Zeppa Fashion — 36</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="C24" s="16">
+        <f>B24*0.124</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Baskets adidas by Stella McCartney UB21 — 36</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>79</v>
-      </c>
-      <c r="C24" s="14">
-        <f>B24*0.124</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f>B24-C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="17" t="n"/>
+      <c r="F24" s="18" t="inlineStr"/>
+      <c r="G24" s="19" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Robe bustier Chiara Ferragni noire — M</t>
+          <t>Baskets adidas by Stella McCartney UB21 — 36</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C25" s="8">
         <f>B25*0.124</f>
@@ -1168,45 +1163,41 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="11" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Robe bustier Chiara Ferragni noire — M</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="C26" s="16">
         <f>B26*0.124</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>Pas Vinted : article neuf</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="n"/>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr"/>
+      <c r="G26" s="19" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
+          <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
@@ -1222,49 +1213,53 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Pas Vinted : article neuf</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="C28" s="16">
+        <f>B28*0.124</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>Orthographe : Pier ANTONIO</t>
         </is>
       </c>
-      <c r="G27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Baskets Geox gris / argent — 35</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n">
-        <v>49</v>
-      </c>
-      <c r="C28" s="14">
-        <f>B28*0.124</f>
-        <v/>
-      </c>
-      <c r="D28" s="15">
-        <f>B28-C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="17" t="n"/>
+      <c r="G28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Morgan — jean bleu clair T.40</t>
+          <t>Baskets Geox gris / argent — 35</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C29" s="8">
         <f>B29*0.124</f>
@@ -1283,38 +1278,38 @@
       <c r="G29" s="11" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Morgan — jupe marron</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Morgan — jean bleu clair T.40</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="16">
         <f>B30*0.124</f>
         <v/>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="17">
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="17" t="n"/>
+      <c r="F30" s="18" t="inlineStr"/>
+      <c r="G30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Morgan — pantalon blanc T.40</t>
+          <t>Morgan — jupe marron</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C31" s="8">
         <f>B31*0.124</f>
@@ -1333,38 +1328,38 @@
       <c r="G31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Morgan — polo rouge à écusson doré L</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Morgan — pantalon blanc T.40</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="16">
         <f>B32*0.124</f>
         <v/>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="17">
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr"/>
-      <c r="G32" s="17" t="n"/>
+      <c r="F32" s="18" t="inlineStr"/>
+      <c r="G32" s="19" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Morgan — top camel lurex L</t>
+          <t>Morgan — polo rouge à écusson doré L</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C33" s="8">
         <f>B33*0.124</f>
@@ -1383,285 +1378,310 @@
       <c r="G33" s="11" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Morgan — top camel lurex L</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C34" s="16">
+        <f>B34*0.124</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr"/>
+      <c r="G34" s="19" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Morgan — polo blanc L</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B35" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C34" s="14">
-        <f>B34*0.124</f>
-        <v/>
-      </c>
-      <c r="D34" s="15">
-        <f>B34-C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="C35" s="8">
+        <f>B35*0.124</f>
+        <v/>
+      </c>
+      <c r="D35" s="9">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="17" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="21" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>New Balance GS 1906 Alkaline Green — 38½</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B37" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C36" s="8">
-        <f>B36*0.124</f>
-        <v/>
-      </c>
-      <c r="D36" s="9">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="C37" s="8">
+        <f>B37*0.124</f>
+        <v/>
+      </c>
+      <c r="D37" s="9">
+        <f>B37-C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Préciser « modèle GS », réf. G19064IK</t>
         </is>
       </c>
-      <c r="G36" s="11" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="G37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B38" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="C37" s="14">
-        <f>B37*0.124</f>
-        <v/>
-      </c>
-      <c r="D37" s="15">
-        <f>B37-C37</f>
-        <v/>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="C38" s="16">
+        <f>B38*0.124</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="17" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr"/>
+      <c r="G38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Tommy Jeans baskets basses noir / blanc — 40</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B39" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C38" s="8">
-        <f>B38*0.124</f>
-        <v/>
-      </c>
-      <c r="D38" s="9">
-        <f>B38-C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="C39" s="8">
+        <f>B39*0.124</f>
+        <v/>
+      </c>
+      <c r="D39" s="9">
+        <f>B39-C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="11" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante — 44</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
+      <c r="B40" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="C39" s="14">
-        <f>B39*0.124</f>
-        <v/>
-      </c>
-      <c r="D39" s="15">
-        <f>B39-C39</f>
-        <v/>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="C40" s="16">
+        <f>B40*0.124</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>B40-C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="17" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr"/>
+      <c r="G40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>New Balance BB80 blanc / marine — 38</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B41" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C40" s="8">
-        <f>B40*0.124</f>
-        <v/>
-      </c>
-      <c r="D40" s="9">
-        <f>B40-C40</f>
-        <v/>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="C41" s="8">
+        <f>B41*0.124</f>
+        <v/>
+      </c>
+      <c r="D41" s="9">
+        <f>B41-C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr"/>
-      <c r="G40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="23" t="n"/>
-      <c r="G41" s="23" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Lot 20 sandales et tongs — EN LOT</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B43" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C42" s="8">
-        <f>B42*0.124</f>
-        <v/>
-      </c>
-      <c r="D42" s="9">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="C43" s="8">
+        <f>B43*0.124</f>
+        <v/>
+      </c>
+      <c r="D43" s="9">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="G42" s="11" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="G43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
         </is>
       </c>
-      <c r="G43" s="17" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="G44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>TOTAL — 34 annonces chiffrées</t>
         </is>
       </c>
-      <c r="B44" s="26">
-        <f>B6+B7+B8+B9+B10+B11+B13+B14+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B36+B37+B38+B39+B40+B42</f>
-        <v/>
-      </c>
-      <c r="C44" s="27">
-        <f>B44*0.124</f>
-        <v/>
-      </c>
-      <c r="D44" s="26">
-        <f>B44-C44</f>
-        <v/>
-      </c>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
-        </is>
-      </c>
+      <c r="B45" s="28">
+        <f>B6+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B37+B38+B39+B40+B41+B43</f>
+        <v/>
+      </c>
+      <c r="C45" s="29">
+        <f>B45*0.124</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="30" t="n"/>
+      <c r="F45" s="30" t="n"/>
+      <c r="G45" s="30" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1280,11 +1280,11 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Morgan — jean bleu clair T.40</t>
+          <t>Robby VP550W pompe immergée 550 W — 1ʳᵉ</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C30" s="16">
         <f>B30*0.124</f>
@@ -1296,20 +1296,24 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr"/>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>TESTER avant de publier · pas d'expédition</t>
+        </is>
+      </c>
       <c r="G30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Morgan — jupe marron</t>
+          <t>Robby VP550W pompe immergée 550 W — 2ᵉ</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C31" s="8">
         <f>B31*0.124</f>
@@ -1321,20 +1325,24 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>À publier quand la 1ʳᵉ est vendue</t>
+        </is>
+      </c>
       <c r="G31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Morgan — pantalon blanc T.40</t>
+          <t>Morgan — jean bleu clair T.40</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C32" s="16">
         <f>B32*0.124</f>
@@ -1355,11 +1363,11 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Morgan — polo rouge à écusson doré L</t>
+          <t>Morgan — jupe marron</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C33" s="8">
         <f>B33*0.124</f>
@@ -1380,11 +1388,11 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Morgan — top camel lurex L</t>
+          <t>Morgan — pantalon blanc T.40</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C34" s="16">
         <f>B34*0.124</f>
@@ -1405,11 +1413,11 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Morgan — polo blanc L</t>
+          <t>Morgan — polo rouge à écusson doré L</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C35" s="8">
         <f>B35*0.124</f>
@@ -1427,27 +1435,39 @@
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="11" t="n"/>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Morgan — top camel lurex L</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" s="16">
+        <f>B36*0.124</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr"/>
+      <c r="G36" s="19" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>New Balance GS 1906 Alkaline Green — 38½</t>
+          <t>Morgan — polo blanc L</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C37" s="8">
         <f>B37*0.124</f>
@@ -1459,49 +1479,33 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>Préciser « modèle GS », réf. G19064IK</t>
-        </is>
-      </c>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="11" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Baskets Emporio Armani bleu lavande — 36</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="C38" s="16">
-        <f>B38*0.124</f>
-        <v/>
-      </c>
-      <c r="D38" s="17">
-        <f>B38-C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr"/>
-      <c r="G38" s="19" t="n"/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Tommy Jeans baskets basses noir / blanc — 40</t>
+          <t>New Balance GS 1906 Alkaline Green — 38½</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C39" s="8">
         <f>B39*0.124</f>
@@ -1513,20 +1517,24 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr"/>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Préciser « modèle GS », réf. G19064IK</t>
+        </is>
+      </c>
       <c r="G39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>New Balance 650 blanche montante — 44</t>
+          <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
       <c r="B40" s="15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C40" s="16">
         <f>B40*0.124</f>
@@ -1547,11 +1555,11 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>New Balance BB80 blanc / marine — 38</t>
+          <t>Tommy Jeans baskets basses noir / blanc — 40</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C41" s="8">
         <f>B41*0.124</f>
@@ -1563,33 +1571,45 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="11" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>4. PLUS TARD — ne pas publier maintenant</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="25" t="n"/>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>New Balance 650 blanche montante — 44</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="C42" s="16">
+        <f>B42*0.124</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr"/>
+      <c r="G42" s="19" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Lot 20 sandales et tongs — EN LOT</t>
+          <t>New Balance BB80 blanc / marine — 38</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>199</v>
+        <v>54</v>
       </c>
       <c r="C43" s="8">
         <f>B43*0.124</f>
@@ -1601,87 +1621,125 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>4. PLUS TARD — ne pas publier maintenant</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Lot 20 sandales et tongs — EN LOT</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>199</v>
+      </c>
+      <c r="C45" s="8">
+        <f>B45*0.124</f>
+        <v/>
+      </c>
+      <c r="D45" s="9">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="G43" s="11" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="G45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
         </is>
       </c>
-      <c r="G44" s="19" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL — 34 annonces chiffrées</t>
-        </is>
-      </c>
-      <c r="B45" s="28">
-        <f>B6+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B37+B38+B39+B40+B41+B43</f>
-        <v/>
-      </c>
-      <c r="C45" s="29">
-        <f>B45*0.124</f>
-        <v/>
-      </c>
-      <c r="D45" s="28">
-        <f>B45-C45</f>
-        <v/>
-      </c>
-      <c r="E45" s="30" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="30" t="n"/>
+      <c r="G46" s="19" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
-        </is>
-      </c>
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL — 36 annonces chiffrées</t>
+        </is>
+      </c>
+      <c r="B47" s="28">
+        <f>B6+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B39+B40+B41+B42+B43+B45</f>
+        <v/>
+      </c>
+      <c r="C47" s="29">
+        <f>B47*0.124</f>
+        <v/>
+      </c>
+      <c r="D47" s="28">
+        <f>B47-C47</f>
+        <v/>
+      </c>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
+      <c r="G47" s="30" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1280,11 +1280,11 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W — 1ʳᵉ</t>
+          <t>Robby VP550W pompe immergée 550 W NEUVE — 1ʳᵉ</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C30" s="16">
         <f>B30*0.124</f>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>TESTER avant de publier · pas d'expédition</t>
+          <t>49 € pendant 10 jours puis 44 € · JAMAIS d'expédition</t>
         </is>
       </c>
       <c r="G30" s="19" t="n"/>
@@ -1309,11 +1309,11 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W — 2ᵉ</t>
+          <t>Robby VP550W pompe immergée 550 W NEUVE — 2ᵉ</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8">
         <f>B31*0.124</f>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1280,11 +1280,11 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W NEUVE — 1ʳᵉ</t>
+          <t>Robby VP550W pompe immergée 550 W — 1ʳᵉ</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" s="16">
         <f>B30*0.124</f>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>49 € pendant 10 jours puis 44 € · JAMAIS d'expédition</t>
+          <t>« Très bon état, jamais utilisée » · JAMAIS d'expédition</t>
         </is>
       </c>
       <c r="G30" s="19" t="n"/>
@@ -1309,11 +1309,11 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W NEUVE — 2ᵉ</t>
+          <t>Robby VP550W pompe immergée 550 W — 2ᵉ</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="8">
         <f>B31*0.124</f>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -90,12 +90,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
+        <fgColor rgb="00F7F7F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F7F7"/>
+        <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
     <fill>
@@ -161,19 +161,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +181,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>✅ VENDU</t>
+          <t>✅ VENDU — 593 €, dont 493 € encaissés</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -636,11 +636,11 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Salomon X Ultra 5 Mid GTX — 44</t>
+          <t>T-shirt Balenciaga — T.2</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C6" s="8">
         <f>B6*0.124</f>
@@ -652,37 +652,53 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>Main propre, espèces</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Encaissé le 09/08 · marge +2,49 € seulement</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Salomon X Ultra 5 Mid GTX — 44</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="14">
+        <f>B7*0.124</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
           <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Vendue le 12/08 · expédier avant le 19/08 20h12</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Vendue le 12/08 · EXPÉDIER AVANT LE 19/08 20h12 · non encaissé</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Havaianas Slim fuchsia 35/36 — LOT de 10 paires</t>
+          <t>Baskets Hoka — 37⅓</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="C8" s="8">
         <f>B8*0.124</f>
@@ -694,49 +710,53 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Main propre, espèces</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Texte d'annonce prêt · plancher 129 €</t>
+          <t>Encaissé le 09/08</t>
         </is>
       </c>
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>75</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Sac demi-lune Karl Lagerfeld Jeans</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" s="14">
         <f>B9*0.124</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="15">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Boutique + Leboncoin</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Main propre, espèces</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Encaissé le 09/08</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
+          <t>Nike Air Max Moto 2K — 44,5</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="C10" s="8">
         <f>B10*0.124</f>
@@ -748,53 +768,53 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Main propre, espèces</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Vérifier marquage CE et notice FR</t>
+          <t>Encaissé le 09/08</t>
         </is>
       </c>
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Lacoste sneakers — 42</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" s="14">
         <f>B11*0.124</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="15">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>Vérifier marquage CE et notice FR</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="n"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Main propre, espèces</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Encaissé le 09/08 · marge +1,44 € seulement</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
+          <t>Veste en jean Armani Exchange — T.S</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C12" s="8">
         <f>B12*0.124</f>
@@ -806,66 +826,66 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Main propre, espèces</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>À publier quand le 1ᵉʳ est vendu</t>
+          <t>Encaissé le 09/08</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="C13" s="16">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Havaianas Slim — 2 paires à 14 €</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="C13" s="14">
         <f>B13*0.124</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="15">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>À publier quand le 1ᵉʳ est vendu</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="n"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Main propre, espèces</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Encaissé le 10/08</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Bottes Forma Legacy Waterproof — 45</t>
+          <t>Havaianas Slim fuchsia 35/36 — LOT de 10 paires</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C15" s="8">
         <f>B15*0.124</f>
@@ -877,53 +897,49 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Boutique + Vinted + Leboncoin</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>À recevoir</t>
+          <t>Texte d'annonce prêt · plancher 129 €</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>BMW Overall ProRain unisexe noir — XL</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>139</v>
-      </c>
-      <c r="C16" s="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="C16" s="14">
         <f>B16*0.124</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="15">
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>À recevoir</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="n"/>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="C17" s="8">
         <f>B17*0.124</f>
@@ -935,53 +951,53 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>Défroisser avant photos</t>
+          <t>Vérifier marquage CE et notice FR</t>
         </is>
       </c>
       <c r="G17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="C18" s="16">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" s="14">
         <f>B18*0.124</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="15">
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>Vérifier composition sur l'étiquette</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="n"/>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Vérifier marquage CE et notice FR</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="C19" s="8">
         <f>B19*0.124</f>
@@ -993,753 +1009,1243 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>À publier quand le 1ᵉʳ est vendu</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="14">
+        <f>B20*0.124</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>À publier quand le 1ᵉʳ est vendu</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bottes Forma Legacy Waterproof — 45</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="C22" s="8">
+        <f>B22*0.124</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Boutique + Vinted + Leboncoin</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>À recevoir</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>BMW Overall ProRain unisexe noir — XL</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>139</v>
+      </c>
+      <c r="C23" s="14">
+        <f>B23*0.124</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>À recevoir</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="C24" s="8">
+        <f>B24*0.124</f>
+        <v/>
+      </c>
+      <c r="D24" s="9">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Défroisser avant photos</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C25" s="14">
+        <f>B25*0.124</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Vérifier composition sur l'étiquette</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="C26" s="8">
+        <f>B26*0.124</f>
+        <v/>
+      </c>
+      <c r="D26" s="9">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Indiquer les deux tailles</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="G26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B27" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="C20" s="16">
-        <f>B20*0.124</f>
-        <v/>
-      </c>
-      <c r="D20" s="17">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="C27" s="14">
+        <f>B27*0.124</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="G20" s="19" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="G27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Adidas Predator Edge.1 TF — 48⅔ — 2ᵉ paire</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B28" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C21" s="8">
-        <f>B21*0.124</f>
-        <v/>
-      </c>
-      <c r="D21" s="9">
-        <f>B21-C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="C28" s="8">
+        <f>B28*0.124</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="G28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Robe Sandro Noaim blanche — 40</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B29" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="C22" s="16">
-        <f>B22*0.124</f>
-        <v/>
-      </c>
-      <c r="D22" s="17">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="C29" s="14">
+        <f>B29*0.124</f>
+        <v/>
+      </c>
+      <c r="D29" s="15">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>Retirer de Vinted d'abord</t>
         </is>
       </c>
-      <c r="G22" s="19" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="G29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Plein Sport montante blanc / violet — 40</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B30" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C23" s="8">
-        <f>B23*0.124</f>
-        <v/>
-      </c>
-      <c r="D23" s="9">
-        <f>B23-C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="C30" s="8">
+        <f>B30*0.124</f>
+        <v/>
+      </c>
+      <c r="D30" s="9">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>99 € pendant 2 semaines, puis 89 €</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="G30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Ballerines Hogan 186 Zeppa Fashion — 36</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B31" s="13" t="n">
         <v>79</v>
       </c>
-      <c r="C24" s="16">
-        <f>B24*0.124</f>
-        <v/>
-      </c>
-      <c r="D24" s="17">
-        <f>B24-C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="C31" s="14">
+        <f>B31*0.124</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr"/>
-      <c r="G24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr"/>
+      <c r="G31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Baskets adidas by Stella McCartney UB21 — 36</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B32" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="C25" s="8">
-        <f>B25*0.124</f>
-        <v/>
-      </c>
-      <c r="D25" s="9">
-        <f>B25-C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="C32" s="8">
+        <f>B32*0.124</f>
+        <v/>
+      </c>
+      <c r="D32" s="9">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Robe bustier Chiara Ferragni noire — M</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B33" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="C26" s="16">
-        <f>B26*0.124</f>
-        <v/>
-      </c>
-      <c r="D26" s="17">
-        <f>B26-C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="C33" s="14">
+        <f>B33*0.124</f>
+        <v/>
+      </c>
+      <c r="D33" s="15">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr"/>
-      <c r="G26" s="19" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr"/>
+      <c r="G33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B34" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="C27" s="8">
-        <f>B27*0.124</f>
-        <v/>
-      </c>
-      <c r="D27" s="9">
-        <f>B27-C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="C34" s="8">
+        <f>B34*0.124</f>
+        <v/>
+      </c>
+      <c r="D34" s="9">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Pas Vinted : article neuf</t>
         </is>
       </c>
-      <c r="G27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="G34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B35" s="13" t="n">
         <v>59</v>
       </c>
-      <c r="C28" s="16">
-        <f>B28*0.124</f>
-        <v/>
-      </c>
-      <c r="D28" s="17">
-        <f>B28-C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="C35" s="14">
+        <f>B35*0.124</f>
+        <v/>
+      </c>
+      <c r="D35" s="15">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Orthographe : Pier ANTONIO</t>
         </is>
       </c>
-      <c r="G28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="G35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Baskets Geox gris / argent — 35</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B36" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="C29" s="8">
-        <f>B29*0.124</f>
-        <v/>
-      </c>
-      <c r="D29" s="9">
-        <f>B29-C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="C36" s="8">
+        <f>B36*0.124</f>
+        <v/>
+      </c>
+      <c r="D36" s="9">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Toupies Beyblade Hasbro — LOT de 4, n°1</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="C37" s="14">
+        <f>B37*0.124</f>
+        <v/>
+      </c>
+      <c r="D37" s="15">
+        <f>B37-C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>Rentrée scolaire : publier avant le 1er septembre</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Toupies Beyblade Hasbro — LOT de 4, n°2</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="8">
+        <f>B38*0.124</f>
+        <v/>
+      </c>
+      <c r="D38" s="9">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>À publier quand le 1er lot est vendu</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Robby VP550W pompe immergée 550 W — 1ʳᵉ</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B39" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="C30" s="16">
-        <f>B30*0.124</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>B30-C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="C39" s="14">
+        <f>B39*0.124</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>B39-C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>« Très bon état, jamais utilisée » · JAMAIS d'expédition</t>
         </is>
       </c>
-      <c r="G30" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="G39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Robby VP550W pompe immergée 550 W — 2ᵉ</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B40" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C31" s="8">
-        <f>B31*0.124</f>
-        <v/>
-      </c>
-      <c r="D31" s="9">
-        <f>B31-C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="C40" s="8">
+        <f>B40*0.124</f>
+        <v/>
+      </c>
+      <c r="D40" s="9">
+        <f>B40-C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>À publier quand la 1ʳᵉ est vendue</t>
         </is>
       </c>
-      <c r="G31" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="G40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Morgan — jean bleu clair T.40</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
+      <c r="B41" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="16">
-        <f>B32*0.124</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
-        <f>B32-C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="C41" s="14">
+        <f>B41*0.124</f>
+        <v/>
+      </c>
+      <c r="D41" s="15">
+        <f>B41-C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr"/>
-      <c r="G32" s="19" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr"/>
+      <c r="G41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Morgan — jupe marron</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B42" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C33" s="8">
-        <f>B33*0.124</f>
-        <v/>
-      </c>
-      <c r="D33" s="9">
-        <f>B33-C33</f>
-        <v/>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="C42" s="8">
+        <f>B42*0.124</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="11" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Morgan — pantalon blanc T.40</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B43" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="C34" s="16">
-        <f>B34*0.124</f>
-        <v/>
-      </c>
-      <c r="D34" s="17">
-        <f>B34-C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="C43" s="14">
+        <f>B43*0.124</f>
+        <v/>
+      </c>
+      <c r="D43" s="15">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr"/>
-      <c r="G34" s="19" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr"/>
+      <c r="G43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Morgan — polo rouge à écusson doré L</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B44" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C35" s="8">
-        <f>B35*0.124</f>
-        <v/>
-      </c>
-      <c r="D35" s="9">
-        <f>B35-C35</f>
-        <v/>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="C44" s="8">
+        <f>B44*0.124</f>
+        <v/>
+      </c>
+      <c r="D44" s="9">
+        <f>B44-C44</f>
+        <v/>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="11" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Morgan — top camel lurex L</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B45" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C36" s="16">
-        <f>B36*0.124</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="C45" s="14">
+        <f>B45*0.124</f>
+        <v/>
+      </c>
+      <c r="D45" s="15">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr"/>
-      <c r="G36" s="19" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr"/>
+      <c r="G45" s="17" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Morgan — polo blanc L</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B46" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C37" s="8">
-        <f>B37*0.124</f>
-        <v/>
-      </c>
-      <c r="D37" s="9">
-        <f>B37-C37</f>
-        <v/>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="C46" s="8">
+        <f>B46*0.124</f>
+        <v/>
+      </c>
+      <c r="D46" s="9">
+        <f>B46-C46</f>
+        <v/>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="23" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>New Balance GS 1906 Alkaline Green — 38½</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B48" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C39" s="8">
-        <f>B39*0.124</f>
-        <v/>
-      </c>
-      <c r="D39" s="9">
-        <f>B39-C39</f>
-        <v/>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="C48" s="8">
+        <f>B48*0.124</f>
+        <v/>
+      </c>
+      <c r="D48" s="9">
+        <f>B48-C48</f>
+        <v/>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Préciser « modèle GS », réf. G19064IK</t>
         </is>
       </c>
-      <c r="G39" s="11" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="G48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B49" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="C40" s="16">
-        <f>B40*0.124</f>
-        <v/>
-      </c>
-      <c r="D40" s="17">
-        <f>B40-C40</f>
-        <v/>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="C49" s="14">
+        <f>B49*0.124</f>
+        <v/>
+      </c>
+      <c r="D49" s="15">
+        <f>B49-C49</f>
+        <v/>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr"/>
-      <c r="G40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr"/>
+      <c r="G49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Tommy Jeans baskets basses noir / blanc — 40</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B50" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C41" s="8">
-        <f>B41*0.124</f>
-        <v/>
-      </c>
-      <c r="D41" s="9">
-        <f>B41-C41</f>
-        <v/>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="C50" s="8">
+        <f>B50*0.124</f>
+        <v/>
+      </c>
+      <c r="D50" s="9">
+        <f>B50-C50</f>
+        <v/>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="11" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante — 44</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
+      <c r="B51" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="C42" s="16">
-        <f>B42*0.124</f>
-        <v/>
-      </c>
-      <c r="D42" s="17">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="C51" s="14">
+        <f>B51*0.124</f>
+        <v/>
+      </c>
+      <c r="D51" s="15">
+        <f>B51-C51</f>
+        <v/>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr"/>
-      <c r="G42" s="19" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr"/>
+      <c r="G51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>New Balance BB80 blanc / marine — 38</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B52" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C43" s="8">
-        <f>B43*0.124</f>
-        <v/>
-      </c>
-      <c r="D43" s="9">
-        <f>B43-C43</f>
-        <v/>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="C52" s="8">
+        <f>B52*0.124</f>
+        <v/>
+      </c>
+      <c r="D52" s="9">
+        <f>B52-C52</f>
+        <v/>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr"/>
-      <c r="G43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>5. POKÉMON — import du Japon, marges minces, vérifier le marché avant de publier</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="23" t="n"/>
+      <c r="G53" s="23" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C54" s="8">
+        <f>B54*0.124</f>
+        <v/>
+      </c>
+      <c r="D54" s="9">
+        <f>B54-C54</f>
+        <v/>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>3,40 €/booster · le moins cher du net est à 3,50 € (Pikastore)</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°2</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" s="14">
+        <f>B55*0.124</f>
+        <v/>
+      </c>
+      <c r="D55" s="15">
+        <f>B55-C55</f>
+        <v/>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>À publier quand le n°1 est vendu</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C56" s="8">
+        <f>B56*0.124</f>
+        <v/>
+      </c>
+      <c r="D56" s="9">
+        <f>B56-C56</f>
+        <v/>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>À publier quand le n°2 est vendu</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°4</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C57" s="14">
+        <f>B57*0.124</f>
+        <v/>
+      </c>
+      <c r="D57" s="15">
+        <f>B57-C57</f>
+        <v/>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>À publier quand le n°3 est vendu</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="8">
+        <f>B58*0.124</f>
+        <v/>
+      </c>
+      <c r="D58" s="9">
+        <f>B58-C58</f>
+        <v/>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>À publier quand le n°4 est vendu</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°6</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" s="14">
+        <f>B59*0.124</f>
+        <v/>
+      </c>
+      <c r="D59" s="15">
+        <f>B59-C59</f>
+        <v/>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>À publier quand le n°5 est vendu</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Booster High Class MEGA Dream ex M2a — à l'unité</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C60" s="8">
+        <f>B60*0.124</f>
+        <v/>
+      </c>
+      <c r="D60" s="9">
+        <f>B60-C60</f>
+        <v/>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>SEUIL 14,78 € · vérifier le prix du booster seul avant de publier</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C61" s="14">
+        <f>B61*0.124</f>
+        <v/>
+      </c>
+      <c r="D61" s="15">
+        <f>B61-C61</f>
+        <v/>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="25" t="n"/>
-      <c r="D44" s="25" t="n"/>
-      <c r="E44" s="25" t="n"/>
-      <c r="F44" s="25" t="n"/>
-      <c r="G44" s="25" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="B62" s="25" t="n"/>
+      <c r="C62" s="25" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="25" t="n"/>
+      <c r="F62" s="25" t="n"/>
+      <c r="G62" s="25" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Lot 20 sandales et tongs — EN LOT</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n">
+      <c r="B63" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C45" s="8">
-        <f>B45*0.124</f>
-        <v/>
-      </c>
-      <c r="D45" s="9">
-        <f>B45-C45</f>
-        <v/>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="C63" s="8">
+        <f>B63*0.124</f>
+        <v/>
+      </c>
+      <c r="D63" s="9">
+        <f>B63-C63</f>
+        <v/>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="G45" s="11" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="G63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
         </is>
       </c>
-      <c r="G46" s="19" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
+      <c r="G64" s="17" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>TOTAL — 36 annonces chiffrées</t>
         </is>
       </c>
-      <c r="B47" s="28">
-        <f>B6+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B39+B40+B41+B42+B43+B45</f>
-        <v/>
-      </c>
-      <c r="C47" s="29">
-        <f>B47*0.124</f>
-        <v/>
-      </c>
-      <c r="D47" s="28">
-        <f>B47-C47</f>
-        <v/>
-      </c>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B65" s="28">
+        <f>B6+B7+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B57+B58+B59+B60+B61+B63</f>
+        <v/>
+      </c>
+      <c r="C65" s="29">
+        <f>B65*0.124</f>
+        <v/>
+      </c>
+      <c r="D65" s="28">
+        <f>B65-C65</f>
+        <v/>
+      </c>
+      <c r="E65" s="30" t="n"/>
+      <c r="F65" s="30" t="n"/>
+      <c r="G65" s="30" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2049,11 +2049,11 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°6</t>
+          <t>BUNDLE : High Class MEGA Dream ex + 5 Nihil Zero</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C59" s="14">
         <f>B59*0.124</f>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>À publier quand le n°5 est vendu</t>
+          <t>Le High Class est INVENDABLE SEUL : marché 12,99 €, coût 12,95 €</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
@@ -2078,11 +2078,11 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Booster High Class MEGA Dream ex M2a — à l'unité</t>
+          <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C60" s="8">
         <f>B60*0.124</f>
@@ -2099,153 +2099,124 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>SEUIL 14,78 € · vérifier le prix du booster seul avant de publier</t>
+          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
         </is>
       </c>
       <c r="G60" s="11" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C61" s="14">
-        <f>B61*0.124</f>
-        <v/>
-      </c>
-      <c r="D61" s="15">
-        <f>B61-C61</f>
-        <v/>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B62" s="25" t="n"/>
-      <c r="C62" s="25" t="n"/>
-      <c r="D62" s="25" t="n"/>
-      <c r="E62" s="25" t="n"/>
-      <c r="F62" s="25" t="n"/>
-      <c r="G62" s="25" t="n"/>
+      <c r="B61" s="25" t="n"/>
+      <c r="C61" s="25" t="n"/>
+      <c r="D61" s="25" t="n"/>
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="25" t="n"/>
+      <c r="G61" s="25" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Lot 20 sandales et tongs — EN LOT</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>199</v>
+      </c>
+      <c r="C62" s="8">
+        <f>B62*0.124</f>
+        <v/>
+      </c>
+      <c r="D62" s="9">
+        <f>B62-C62</f>
+        <v/>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin B2B</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Lot 20 sandales et tongs — EN LOT</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n">
-        <v>199</v>
-      </c>
-      <c r="C63" s="8">
-        <f>B63*0.124</f>
-        <v/>
-      </c>
-      <c r="D63" s="9">
-        <f>B63-C63</f>
-        <v/>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin B2B</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="n"/>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Vinted</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Vinted</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="27" t="inlineStr">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>TOTAL — 36 annonces chiffrées</t>
         </is>
       </c>
-      <c r="B65" s="28">
-        <f>B6+B7+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B57+B58+B59+B60+B61+B63</f>
-        <v/>
-      </c>
-      <c r="C65" s="29">
-        <f>B65*0.124</f>
-        <v/>
-      </c>
-      <c r="D65" s="28">
-        <f>B65-C65</f>
-        <v/>
-      </c>
-      <c r="E65" s="30" t="n"/>
-      <c r="F65" s="30" t="n"/>
-      <c r="G65" s="30" t="n"/>
+      <c r="B64" s="28">
+        <f>B6+B7+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B57+B58+B59+B60+B62</f>
+        <v/>
+      </c>
+      <c r="C64" s="29">
+        <f>B64*0.124</f>
+        <v/>
+      </c>
+      <c r="D64" s="28">
+        <f>B64-C64</f>
+        <v/>
+      </c>
+      <c r="E64" s="30" t="n"/>
+      <c r="F64" s="30" t="n"/>
+      <c r="G64" s="30" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
+          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1541,11 +1541,11 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W — 1ʳᵉ</t>
+          <t>Robby VP550W pompe immergée — ligne 84, occasion</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C39" s="14">
         <f>B39*0.124</f>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>« Très bon état, jamais utilisée » · JAMAIS d'expédition</t>
+          <t>Tester avant de publier · JAMAIS d'expédition, 4,8 kg</t>
         </is>
       </c>
       <c r="G39" s="17" t="n"/>
@@ -1570,11 +1570,11 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée 550 W — 2ᵉ</t>
+          <t>Robby VP550W pompe immergée — ligne 122, SOCLE CASSÉ</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C40" s="8">
         <f>B40*0.124</f>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>À publier quand la 1ʳᵉ est vendue</t>
+          <t>DÉFAUT À DÉCLARER + photo du socle · JAMAIS d'expédition</t>
         </is>
       </c>
       <c r="G40" s="11" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -2049,11 +2049,11 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>BUNDLE : High Class MEGA Dream ex + 5 Nihil Zero</t>
+          <t>Boosters Nihil Zero M3 — LOT de 5, n°6</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C59" s="14">
         <f>B59*0.124</f>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>Le High Class est INVENDABLE SEUL : marché 12,99 €, coût 12,95 €</t>
+          <t>À publier quand le n°5 est vendu</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1891,7 +1891,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>5. POKÉMON — import du Japon, marges minces, vérifier le marché avant de publier</t>
+          <t>5. POKÉMON — import du Japon, marges minces</t>
         </is>
       </c>
       <c r="B53" s="23" t="n"/>
@@ -1904,11 +1904,11 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°1</t>
+          <t>Boosters Nihil Zero M3 — LOT de 15, n°1</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C54" s="8">
         <f>B54*0.124</f>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>3,40 €/booster · le moins cher du net est à 3,50 € (Pikastore)</t>
+          <t>PHOTOGRAPHIER LE BLISTER SCELLÉ avant d'ouvrir la box</t>
         </is>
       </c>
       <c r="G54" s="11" t="n"/>
@@ -1933,11 +1933,11 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°2</t>
+          <t>Boosters Nihil Zero M3 — LOT de 15, n°2</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C55" s="14">
         <f>B55*0.124</f>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>À publier quand le n°1 est vendu</t>
+          <t>« Boosters non pesés, non triés » dans l'annonce</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
@@ -1962,11 +1962,11 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°3</t>
+          <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C56" s="8">
         <f>B56*0.124</f>
@@ -1983,48 +1983,32 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>À publier quand le n°2 est vendu</t>
+          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
         </is>
       </c>
       <c r="G56" s="11" t="n"/>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°4</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="C57" s="14">
-        <f>B57*0.124</f>
-        <v/>
-      </c>
-      <c r="D57" s="15">
-        <f>B57-C57</f>
-        <v/>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>À publier quand le n°3 est vendu</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="n"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>4. PLUS TARD — ne pas publier maintenant</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="25" t="n"/>
+      <c r="D57" s="25" t="n"/>
+      <c r="E57" s="25" t="n"/>
+      <c r="F57" s="25" t="n"/>
+      <c r="G57" s="25" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°5</t>
+          <t>Lot 20 sandales et tongs — EN LOT</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C58" s="8">
         <f>B58*0.124</f>
@@ -2036,12 +2020,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Leboncoin B2B</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>À publier quand le n°4 est vendu</t>
+          <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
       <c r="G58" s="11" t="n"/>
@@ -2049,174 +2033,74 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 5, n°6</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="C59" s="14">
-        <f>B59*0.124</f>
-        <v/>
-      </c>
-      <c r="D59" s="15">
-        <f>B59-C59</f>
-        <v/>
+          <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>À publier quand le n°5 est vendu</t>
+          <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C60" s="8">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL — 36 annonces chiffrées</t>
+        </is>
+      </c>
+      <c r="B60" s="28">
+        <f>B6+B7+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B58</f>
+        <v/>
+      </c>
+      <c r="C60" s="29">
         <f>B60*0.124</f>
         <v/>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="28">
         <f>B60-C60</f>
         <v/>
       </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
-        <is>
-          <t>4. PLUS TARD — ne pas publier maintenant</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="n"/>
-      <c r="C61" s="25" t="n"/>
-      <c r="D61" s="25" t="n"/>
-      <c r="E61" s="25" t="n"/>
-      <c r="F61" s="25" t="n"/>
-      <c r="G61" s="25" t="n"/>
+      <c r="E60" s="30" t="n"/>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="30" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Lot 20 sandales et tongs — EN LOT</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n">
-        <v>199</v>
-      </c>
-      <c r="C62" s="8">
-        <f>B62*0.124</f>
-        <v/>
-      </c>
-      <c r="D62" s="9">
-        <f>B62-C62</f>
-        <v/>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin B2B</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
-        </is>
-      </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>Vinted</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL — 36 annonces chiffrées</t>
-        </is>
-      </c>
-      <c r="B64" s="28">
-        <f>B6+B7+B8+B9+B10+B11+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B57+B58+B59+B60+B62</f>
-        <v/>
-      </c>
-      <c r="C64" s="29">
-        <f>B64*0.124</f>
-        <v/>
-      </c>
-      <c r="D64" s="28">
-        <f>B64-C64</f>
-        <v/>
-      </c>
-      <c r="E64" s="30" t="n"/>
-      <c r="F64" s="30" t="n"/>
-      <c r="G64" s="30" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -843,7 +843,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Havaianas Slim — paire 2, « Vintage Go »</t>
+          <t>Havaianas Slim — paire 2, « colline_dvl »</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1487,7 +1487,7 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Toupies Beyblade Hasbro — LOT de 4, n°1</t>
+          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°159</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>Rentrée scolaire : publier avant le 1er septembre</t>
+          <t>Coût 21,54 € · marge 21,39 € · publier avant le 1er septembre</t>
         </is>
       </c>
       <c r="G37" s="17" t="n"/>
@@ -1516,7 +1516,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Toupies Beyblade Hasbro — LOT de 4, n°2</t>
+          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°299</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>À publier quand le 1er lot est vendu</t>
+          <t>Coût 40,71 € · marge 2,22 € seulement · à publier après le n°159</t>
         </is>
       </c>
       <c r="G38" s="11" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1348,7 +1348,11 @@
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr"/>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Nettoyées : « aucune trace visible », PAS « neuves » — 12 mois de garantie au lieu de 24</t>
+        </is>
+      </c>
       <c r="G31" s="17" t="n"/>
     </row>
     <row r="32">

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C45" s="14">
         <f>B45*0.124</f>
@@ -1726,7 +1726,11 @@
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr"/>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>Remonté de 12 à 15 € : 12 € passait sous le plancher</t>
+        </is>
+      </c>
       <c r="G45" s="17" t="n"/>
     </row>
     <row r="46">
@@ -1736,7 +1740,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C46" s="8">
         <f>B46*0.124</f>
@@ -1751,7 +1755,11 @@
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Remonté de 12 à 15 € : 12 € passait sous le plancher</t>
+        </is>
+      </c>
       <c r="G46" s="11" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -71,7 +71,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -90,12 +90,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FBDDD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7F7F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F0DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +163,9 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -161,37 +174,43 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -557,16 +576,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,25 +616,30 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>MARGE / VENTE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>URSSAF 12,4 %</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Reste après URSSAF</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Où le vendre</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Fait</t>
         </is>
@@ -632,6 +657,7 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -642,54 +668,60 @@
       <c r="B6" s="7" t="n">
         <v>135</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D6" s="9">
         <f>B6*0.124</f>
         <v/>
       </c>
-      <c r="D6" s="9">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="10">
+        <f>B6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Mme Aouimeur Siham, espèces</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Encaissé le 09/08 · marge +2,49 € seulement</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Salomon X Ultra 5 Mid GTX — 44</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="8" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D7" s="15">
         <f>B7*0.124</f>
         <v/>
       </c>
-      <c r="D7" s="15">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="16">
+        <f>B7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Vendue le 12/08 · EXPÉDIER AVANT LE 19/08 20h12 · non encaissé</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -700,54 +732,60 @@
       <c r="B8" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="8" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D8" s="9">
         <f>B8*0.124</f>
         <v/>
       </c>
-      <c r="D8" s="9">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="10">
+        <f>B8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Mme Aouimeur Siham, espèces</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Encaissé le 09/08</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Lacoste sneakers — 42</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D9" s="15">
         <f>B9*0.124</f>
         <v/>
       </c>
-      <c r="D9" s="15">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="16">
+        <f>B9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Mme Aouimeur Siham, espèces</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Encaissé le 09/08 · marge +1,44 € seulement</t>
         </is>
       </c>
-      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -758,58 +796,66 @@
       <c r="B10" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="8" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="D10" s="9">
         <f>B10*0.124</f>
         <v/>
       </c>
-      <c r="D10" s="9">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="10">
+        <f>B10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Mme Aouimeur Siham, espèces</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Encaissé le 09/08</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>— Hoka 37⅓ et Nike Air Max Moto : PRÉLÈVEMENTS, pas des ventes</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Usage personnel</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>HORS CA : ne pas déclarer les 150 €</t>
         </is>
       </c>
-      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -820,67 +866,74 @@
       <c r="B12" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D12" s="9">
         <f>B12*0.124</f>
         <v/>
       </c>
-      <c r="D12" s="9">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="10">
+        <f>B12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Expédiée le 03/08 · encaissée le 10/08 · trop bas, passer à 18 €</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Havaianas Slim — paire 2, « colline_dvl »</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D13" s="15">
         <f>B13*0.124</f>
         <v/>
       </c>
-      <c r="D13" s="15">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="16">
+        <f>B13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Encaissée le 10/08 · trop bas, passer à 18 €</t>
         </is>
       </c>
-      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="18" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -891,50 +944,60 @@
       <c r="B15" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="8" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D15" s="9">
         <f>B15*0.124</f>
         <v/>
       </c>
-      <c r="D15" s="9">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="10">
+        <f>B15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Vinted + Leboncoin</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>À L'UNITÉ, pas en lot · plancher 16 € · 50 € de marge sur les 10</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Moins cher du net 15 €/paire · 25 € par vente HORS D'ATTEINTE</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="8" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="D16" s="15">
         <f>B16*0.124</f>
         <v/>
       </c>
-      <c r="D16" s="15">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="16">
+        <f>B16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="17" t="n"/>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Moins cher du net ~75 € Modz · plafonné, ne peut pas monter</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -943,56 +1006,62 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C17" s="8">
+        <v>34</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D17" s="9">
         <f>B17*0.124</f>
         <v/>
       </c>
-      <c r="D17" s="9">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="10">
+        <f>B17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Vérifier marquage CE et notice FR</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="n"/>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D18" s="15">
         <f>B18*0.124</f>
         <v/>
       </c>
-      <c r="D18" s="15">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="16">
+        <f>B18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Vérifier marquage CE et notice FR</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="n"/>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1001,69 +1070,76 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C19" s="8">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D19" s="9">
         <f>B19*0.124</f>
         <v/>
       </c>
-      <c r="D19" s="9">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="10">
+        <f>B19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D20" s="15">
         <f>B20*0.124</f>
         <v/>
       </c>
-      <c r="D20" s="15">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="16">
+        <f>B20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>À publier quand le 1ᵉʳ est vendu</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>OU les quatre en un lot à 136 € : 71,87 € en une seule vente</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1074,54 +1150,60 @@
       <c r="B22" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="25" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="D22" s="9">
         <f>B22*0.124</f>
         <v/>
       </c>
-      <c r="D22" s="9">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="10">
+        <f>B22-D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Boutique + Vinted + Leboncoin</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>À recevoir</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="n"/>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Neuves 172,49 € Dafy Moto</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BMW Overall ProRain unisexe noir — XL</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>139</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="25" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="D23" s="15">
         <f>B23*0.124</f>
         <v/>
       </c>
-      <c r="D23" s="15">
-        <f>B23-C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="16">
+        <f>B23-D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>À recevoir</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="n"/>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Neuf 170 €</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1132,54 +1214,60 @@
       <c r="B24" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="25" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="D24" s="9">
         <f>B24*0.124</f>
         <v/>
       </c>
-      <c r="D24" s="9">
-        <f>B24-C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="10">
+        <f>B24-D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Défroisser avant photos</t>
         </is>
       </c>
-      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="25" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="D25" s="15">
         <f>B25*0.124</f>
         <v/>
       </c>
-      <c r="D25" s="15">
-        <f>B25-C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="16">
+        <f>B25-D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>Vérifier composition sur l'étiquette</t>
         </is>
       </c>
-      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1188,56 +1276,62 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="D26" s="9">
+        <f>B26*0.124</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>B26-D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>89 → 91 € · neuf dès 229 € Modalova — À RECONFIRMER avant publication</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
         <v>89</v>
       </c>
-      <c r="C26" s="8">
-        <f>B26*0.124</f>
-        <v/>
-      </c>
-      <c r="D26" s="9">
-        <f>B26-C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Indiquer les deux tailles</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="C27" s="14">
+      <c r="C27" s="25" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D27" s="15">
         <f>B27*0.124</f>
         <v/>
       </c>
-      <c r="D27" s="15">
-        <f>B27-C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="16">
+        <f>B27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1248,54 +1342,60 @@
       <c r="B28" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="25" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D28" s="9">
         <f>B28*0.124</f>
         <v/>
       </c>
-      <c r="D28" s="9">
-        <f>B28-C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="10">
+        <f>B28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="12" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Robe Sandro Noaim blanche — 40</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="14" t="n">
         <v>89</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="25" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="D29" s="15">
         <f>B29*0.124</f>
         <v/>
       </c>
-      <c r="D29" s="15">
-        <f>B29-C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="16">
+        <f>B29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>Retirer de Vinted d'abord</t>
         </is>
       </c>
-      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1304,56 +1404,62 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="C30" s="8">
+        <v>95</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="D30" s="9">
         <f>B30*0.124</f>
         <v/>
       </c>
-      <c r="D30" s="9">
-        <f>B30-C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="10">
+        <f>B30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>99 € pendant 2 semaines, puis 89 €</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="n"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>89 → 95 € · marché ~100 € Stylight, VÉRIFIER avant de publier</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Ballerines Hogan 186 Zeppa Fashion — 36</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="14" t="n">
         <v>79</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="25" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="D31" s="15">
         <f>B31*0.124</f>
         <v/>
       </c>
-      <c r="D31" s="15">
-        <f>B31-C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="16">
+        <f>B31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>Nettoyées : « aucune trace visible », PAS « neuves » — 12 mois de garantie au lieu de 24</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="n"/>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Nettoyées : « aucune trace visible », PAS « neuves »</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1364,416 +1470,470 @@
       <c r="B32" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="25" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="D32" s="9">
         <f>B32*0.124</f>
         <v/>
       </c>
-      <c r="D32" s="9">
-        <f>B32-C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="10">
+        <f>B32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Neuf 94 € eBay.de</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Robe bustier Chiara Ferragni noire — M</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="25" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="D33" s="15">
         <f>B33*0.124</f>
         <v/>
       </c>
-      <c r="D33" s="15">
-        <f>B33-C33</f>
-        <v/>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="16">
+        <f>B33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="17" t="n"/>
+      <c r="G33" s="17" t="inlineStr"/>
+      <c r="H33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
+          <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="D34" s="9">
+        <f>B34*0.124</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>B34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>59 → 62 € · orthographe : Pier ANTONIO</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
           <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="C34" s="8">
-        <f>B34*0.124</f>
-        <v/>
-      </c>
-      <c r="D34" s="9">
-        <f>B34-C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="B35" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="D35" s="15">
+        <f>B35*0.124</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>B35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Pas Vinted : article neuf</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="C35" s="14">
-        <f>B35*0.124</f>
-        <v/>
-      </c>
-      <c r="D35" s="15">
-        <f>B35-C35</f>
-        <v/>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Boutique + Leboncoin</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Orthographe : Pier ANTONIO</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="n"/>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>59 → 61 € · marché 70 € · pas Vinted : article neuf</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°159</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C36" s="25" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="D36" s="9">
+        <f>B36*0.124</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>B36-D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>49 → 55 € · CONFIRMER le prix des 4 toupies sur leDénicheur</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
           <t>Baskets Geox gris / argent — 35</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="C36" s="8">
-        <f>B36*0.124</f>
-        <v/>
-      </c>
-      <c r="D36" s="9">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="B37" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D37" s="15">
+        <f>B37*0.124</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>B37-D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="11" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°159</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="n">
-        <v>49</v>
-      </c>
-      <c r="C37" s="14">
-        <f>B37*0.124</f>
-        <v/>
-      </c>
-      <c r="D37" s="15">
-        <f>B37-C37</f>
-        <v/>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Coût 21,54 € · marge 21,39 € · publier avant le 1er septembre</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="n"/>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>49 → 54 € · marché 55 €, plafond atteint</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°299</t>
+          <t>Morgan — jean bleu clair T.40</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="C38" s="8">
+        <v>19</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="D38" s="9">
         <f>B38*0.124</f>
         <v/>
       </c>
-      <c r="D38" s="9">
-        <f>B38-C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Coût 40,71 € · marge 2,22 € seulement · à publier après le n°159</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="n"/>
+      <c r="E38" s="10">
+        <f>B38-D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>À l'unité : 25 € par vente impossible</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Robby VP550W pompe immergée — ligne 84, occasion</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="C39" s="14">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Morgan — jupe marron</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="D39" s="15">
         <f>B39*0.124</f>
         <v/>
       </c>
-      <c r="D39" s="15">
-        <f>B39-C39</f>
-        <v/>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>Tester avant de publier · JAMAIS d'expédition, 4,8 kg</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="n"/>
+      <c r="E39" s="16">
+        <f>B39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr"/>
+      <c r="H39" s="18" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Robby VP550W pompe immergée — ligne 122, SOCLE CASSÉ</t>
+          <t>Morgan — pantalon blanc T.40</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="C40" s="8">
+        <v>15</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D40" s="9">
         <f>B40*0.124</f>
         <v/>
       </c>
-      <c r="D40" s="9">
-        <f>B40-C40</f>
-        <v/>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>DÉFAUT À DÉCLARER + photo du socle · JAMAIS d'expédition</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="n"/>
+      <c r="E40" s="10">
+        <f>B40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="12" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Morgan — jean bleu clair T.40</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C41" s="14">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Morgan — polo rouge à écusson doré L</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D41" s="15">
         <f>B41*0.124</f>
         <v/>
       </c>
-      <c r="D41" s="15">
-        <f>B41-C41</f>
-        <v/>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="16">
+        <f>B41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="17" t="n"/>
+      <c r="G41" s="17" t="inlineStr"/>
+      <c r="H41" s="18" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Morgan — jupe marron</t>
+          <t>Morgan — top camel lurex L</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C42" s="8">
+        <v>15</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D42" s="9">
         <f>B42*0.124</f>
         <v/>
       </c>
-      <c r="D42" s="9">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="10">
+        <f>B42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>OU les six en un lot à 98 € : 33,85 € en une seule vente</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>Morgan — pantalon blanc T.40</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="n">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Morgan — polo blanc L</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D43" s="15">
         <f>B43*0.124</f>
         <v/>
       </c>
-      <c r="D43" s="15">
-        <f>B43-C43</f>
-        <v/>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="16">
+        <f>B43-D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr"/>
-      <c r="G43" s="17" t="n"/>
+      <c r="G43" s="17" t="inlineStr"/>
+      <c r="H43" s="18" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Morgan — polo rouge à écusson doré L</t>
+          <t>Robby VP550W pompe immergée — ligne 84, occasion</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C44" s="8">
+        <v>45</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="D44" s="9">
         <f>B44*0.124</f>
         <v/>
       </c>
-      <c r="D44" s="9">
-        <f>B44-C44</f>
-        <v/>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="11" t="n"/>
+      <c r="E44" s="10">
+        <f>B44-D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Neuve 54,90 € : plafonné · tester avant de publier</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>Morgan — top camel lurex L</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C45" s="14">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Robby VP550W pompe immergée — ligne 122, SOCLE CASSÉ</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D45" s="15">
         <f>B45*0.124</f>
         <v/>
       </c>
-      <c r="D45" s="15">
-        <f>B45-C45</f>
-        <v/>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>Remonté de 12 à 15 € : 12 € passait sous le plancher</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="n"/>
+      <c r="E45" s="16">
+        <f>B45-D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>DÉFAUT À DÉCLARER + photo du socle · JAMAIS d'expédition</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Morgan — polo blanc L</t>
+          <t>Toupies Beyblade Hasbro — LOT de 4, lot n°299</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C46" s="8">
+        <v>55</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="D46" s="9">
         <f>B46*0.124</f>
         <v/>
       </c>
-      <c r="D46" s="9">
-        <f>B46-C46</f>
-        <v/>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>Remonté de 12 à 15 € : 12 € passait sous le plancher</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="n"/>
+      <c r="E46" s="10">
+        <f>B46-D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Payé 40,71 € au lieu de 21,54 € : le lot jumeau plafonne la marge</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
         </is>
       </c>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="24" t="n"/>
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
+      <c r="H47" s="27" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -1784,50 +1944,60 @@
       <c r="B48" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="8" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="D48" s="9">
         <f>B48*0.124</f>
         <v/>
       </c>
-      <c r="D48" s="9">
-        <f>B48-C48</f>
-        <v/>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="10">
+        <f>B48-D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>Préciser « modèle GS », réf. G19064IK</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="n"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>AU-DESSUS du marché 87 € StockX — à trancher</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n">
+      <c r="B49" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="8" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="D49" s="15">
         <f>B49*0.124</f>
         <v/>
       </c>
-      <c r="D49" s="15">
-        <f>B49-C49</f>
-        <v/>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="16">
+        <f>B49-D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr"/>
-      <c r="G49" s="17" t="n"/>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>AU-DESSUS du marché 62 € eBay — à trancher</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -1838,46 +2008,60 @@
       <c r="B50" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D50" s="9">
         <f>B50*0.124</f>
         <v/>
       </c>
-      <c r="D50" s="9">
-        <f>B50-C50</f>
-        <v/>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="10">
+        <f>B50-D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr"/>
-      <c r="G50" s="11" t="n"/>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>AU-DESSUS du marché 60 € Stylight — à trancher</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante — 44</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n">
+      <c r="B51" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D51" s="15">
         <f>B51*0.124</f>
         <v/>
       </c>
-      <c r="D51" s="15">
-        <f>B51-C51</f>
-        <v/>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="16">
+        <f>B51-D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr"/>
-      <c r="G51" s="17" t="n"/>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>AU-DESSUS du marché 61 € idealo — à trancher</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -1888,34 +2072,42 @@
       <c r="B52" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D52" s="9">
         <f>B52*0.124</f>
         <v/>
       </c>
-      <c r="D52" s="9">
-        <f>B52-C52</f>
-        <v/>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="10">
+        <f>B52-D52</f>
+        <v/>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr"/>
-      <c r="G52" s="11" t="n"/>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Marché 54,99 € idealo : plafond atteint</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>5. POKÉMON — import du Japon, marges minces</t>
         </is>
       </c>
-      <c r="B53" s="24" t="n"/>
-      <c r="C53" s="24" t="n"/>
-      <c r="D53" s="24" t="n"/>
-      <c r="E53" s="24" t="n"/>
-      <c r="F53" s="24" t="n"/>
-      <c r="G53" s="24" t="n"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="27" t="n"/>
+      <c r="H53" s="27" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -1926,54 +2118,60 @@
       <c r="B54" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D54" s="9">
         <f>B54*0.124</f>
         <v/>
       </c>
-      <c r="D54" s="9">
-        <f>B54-C54</f>
-        <v/>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="10">
+        <f>B54-D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>PHOTOGRAPHIER LE BLISTER SCELLÉ avant d'ouvrir la box</t>
         </is>
       </c>
-      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="12" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Boosters Nihil Zero M3 — LOT de 15, n°2</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n">
+      <c r="B55" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D55" s="15">
         <f>B55*0.124</f>
         <v/>
       </c>
-      <c r="D55" s="15">
-        <f>B55-C55</f>
-        <v/>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="16">
+        <f>B55-D55</f>
+        <v/>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
         <is>
           <t>« Boosters non pesés, non triés » dans l'annonce</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="18" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -1984,38 +2182,42 @@
       <c r="B56" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D56" s="9">
         <f>B56*0.124</f>
         <v/>
       </c>
-      <c r="D56" s="9">
-        <f>B56-C56</f>
-        <v/>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="10">
+        <f>B56-D56</f>
+        <v/>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>SEUIL 14,54 € · set sorti le 31/07/2026, forte demande</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="n"/>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Set sorti le 31/07/2026, forte demande</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B57" s="26" t="n"/>
-      <c r="C57" s="26" t="n"/>
-      <c r="D57" s="26" t="n"/>
-      <c r="E57" s="26" t="n"/>
-      <c r="F57" s="26" t="n"/>
-      <c r="G57" s="26" t="n"/>
+      <c r="B57" s="29" t="n"/>
+      <c r="C57" s="29" t="n"/>
+      <c r="D57" s="29" t="n"/>
+      <c r="E57" s="29" t="n"/>
+      <c r="F57" s="29" t="n"/>
+      <c r="G57" s="29" t="n"/>
+      <c r="H57" s="29" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2026,92 +2228,98 @@
       <c r="B58" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="25" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="D58" s="9">
         <f>B58*0.124</f>
         <v/>
       </c>
-      <c r="D58" s="9">
-        <f>B58-C58</f>
-        <v/>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="10">
+        <f>B58-D58</f>
+        <v/>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="12" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B59" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="B59" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="C59" s="25" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="D59" s="15">
+        <f>B59*0.124</f>
+        <v/>
+      </c>
+      <c r="E59" s="16">
+        <f>B59-D59</f>
+        <v/>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>BLOQUÉ : authentification requise avant de fixer le prix</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n"/>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>Neuve 140 € wehaveit.fr · prix valable SI l'authentification passe</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL — 36 annonces chiffrées</t>
-        </is>
-      </c>
-      <c r="B60" s="28">
-        <f>B6+B7+B8+B9+B10+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B58</f>
-        <v/>
-      </c>
-      <c r="C60" s="29">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL — 48 annonces chiffrées</t>
+        </is>
+      </c>
+      <c r="B60" s="31">
+        <f>B6+B7+B8+B9+B10+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B58+B59</f>
+        <v/>
+      </c>
+      <c r="C60" s="31">
+        <f>C6+C7+C8+C9+C10+C12+C13+C15+C16+C17+C18+C19+C20+C22+C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C48+C49+C50+C51+C52+C54+C55+C56+C58+C59</f>
+        <v/>
+      </c>
+      <c r="D60" s="32">
         <f>B60*0.124</f>
         <v/>
       </c>
-      <c r="D60" s="28">
-        <f>B60-C60</f>
-        <v/>
-      </c>
-      <c r="E60" s="30" t="n"/>
-      <c r="F60" s="30" t="n"/>
-      <c r="G60" s="30" t="n"/>
+      <c r="E60" s="31">
+        <f>B60-D60</f>
+        <v/>
+      </c>
+      <c r="F60" s="33" t="n"/>
+      <c r="G60" s="33" t="n"/>
+      <c r="H60" s="33" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Le prix de la Yeezy sera fixé après authentification (10-20 €).</t>
+          <t>MARGE / VENTE en vert : l'objectif de 25 € par vente est atteint. En rouge : le prix de rue plafonne, il ne peut pas l'être.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Règle : ces prix sont déjà calés sous le moins cher trouvé sur Internet. Ne pas les remonter.</t>
+          <t>Règle : ces prix sont calés SOUS le moins cher trouvé sur Internet. Quatre lignes en « Liquider » sont au-dessus — décision à prendre.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Vendue le 12/08 · EXPÉDIER AVANT LE 19/08 20h12 · non encaissé</t>
+          <t>Vendue le 12/08 · EXPÉDIÉE le 14/08, locker Mondial Relay · en attente d'encaissement</t>
         </is>
       </c>
       <c r="H7" s="18" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -71,7 +71,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005D6D7E"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,31 +191,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -822,37 +829,31 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>— Hoka 37⅓ et Nike Air Max Moto : PRÉLÈVEMENTS, pas des ventes</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Havaianas Slim — paire 1, N. Gulitz (Allemagne)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D11" s="15">
+        <f>B11*0.124</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>B11-D11</f>
+        <v/>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Usage personnel</t>
+          <t>Vinted</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>HORS CA : ne pas déclarer les 150 €</t>
+          <t>Expédiée le 03/08 · encaissée le 10/08 · trop bas, passer à 18 €</t>
         </is>
       </c>
       <c r="H11" s="18" t="n"/>
@@ -860,7 +861,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Havaianas Slim — paire 1, N. Gulitz (Allemagne)</t>
+          <t>Havaianas Slim — paire 2, « colline_dvl »</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -884,274 +885,304 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Expédiée le 03/08 · encaissée le 10/08 · trop bas, passer à 18 €</t>
+          <t>Encaissée le 10/08 · trop bas, passer à 18 €</t>
         </is>
       </c>
       <c r="H12" s="12" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Havaianas Slim — paire 2, « colline_dvl »</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="D13" s="15">
-        <f>B13*0.124</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>B13-D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Vinted</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>Encaissée le 10/08 · trop bas, passer à 18 €</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>🏠 PRÉLEVÉ — usage personnel, HORS chiffre d’affaires</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37⅓ — neuves</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Gardées le 09/08</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Coût 65,37 € · aucune recette, aucune URSSAF · sortie au registre des objets mobiliers</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Baskets NIKE Air Max Moto 2K P.44,5 — neuves</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Gardées le 09/08</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Coût 52,77 € · aucune recette, aucune URSSAF · sortie au registre des objets mobiliers</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Pompe ROBBY VP550W — ligne 131, mode auto seulement</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Gardée le 13/08</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Coût 19,41 € · la 3ᵉ pompe : deux sont à vendre, celle-ci est à toi</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Booster Pokémon High Class MEGA Dream ex M2a</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Gardé le 13/08</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Coût 12,95 € · invendable avec profit : marché à 12,99 €</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>— TOTAL PRÉLEVÉ : 150,50 €, remboursé au compte pro en apport</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Apport, pas recette</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>NE PAS DÉCLARER À L'URSSAF · un micro-entrepreneur ne se vend pas à lui-même</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>1. URGENT — à publier cette semaine, la saison finit fin septembre</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Havaianas Slim fuchsia 35/36 — à l'unité, 10 restantes</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C20" s="8" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="9">
-        <f>B15*0.124</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>B15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D20" s="9">
+        <f>B20*0.124</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>B20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Vinted + Leboncoin</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Moins cher du net 15 €/paire · 25 € par vente HORS D'ATTEINTE</t>
         </is>
       </c>
-      <c r="H15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="H20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Short ba&amp;sh Fegor lightusedblue — T.34</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B21" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C21" s="8" t="n">
         <v>11.81</v>
       </c>
-      <c r="D16" s="15">
-        <f>B16*0.124</f>
-        <v/>
-      </c>
-      <c r="E16" s="16">
-        <f>B16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="D21" s="15">
+        <f>B21*0.124</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>B21-D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Moins cher du net ~75 € Modz · plafonné, ne peut pas monter</t>
         </is>
       </c>
-      <c r="H16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="D17" s="9">
-        <f>B17*0.124</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>B17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="D18" s="15">
-        <f>B18*0.124</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>B18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="D19" s="9">
-        <f>B19*0.124</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>B19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>À publier quand le 1ᵉʳ est vendu</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="D20" s="15">
-        <f>B20*0.124</f>
-        <v/>
-      </c>
-      <c r="E20" s="16">
-        <f>B20-D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>OU les quatre en un lot à 136 € : 71,87 € en une seule vente</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
+      <c r="H21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bottes Forma Legacy Waterproof — 45</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle écru</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="C22" s="25" t="n">
-        <v>71.53</v>
+        <v>34</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>17.96</v>
       </c>
       <c r="D22" s="9">
         <f>B22*0.124</f>
@@ -1163,12 +1194,12 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Boutique + Vinted + Leboncoin</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Neuves 172,49 € Dafy Moto</t>
+          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
         </is>
       </c>
       <c r="H22" s="12" t="n"/>
@@ -1176,14 +1207,14 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>BMW Overall ProRain unisexe noir — XL</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — modèle vichy</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>50.83</v>
+        <v>34</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>17.96</v>
       </c>
       <c r="D23" s="15">
         <f>B23*0.124</f>
@@ -1200,7 +1231,7 @@
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Neuf 170 €</t>
+          <t>PRIX CORRIGÉ 19 → 34 € · neuf 37,50 € · vérifier marquage CE</t>
         </is>
       </c>
       <c r="H23" s="18" t="n"/>
@@ -1208,14 +1239,14 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ écru</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="C24" s="25" t="n">
-        <v>62.42</v>
+        <v>34</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>17.96</v>
       </c>
       <c r="D24" s="9">
         <f>B24*0.124</f>
@@ -1227,12 +1258,12 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Défroisser avant photos</t>
+          <t>À publier quand le 1ᵉʳ est vendu</t>
         </is>
       </c>
       <c r="H24" s="12" t="n"/>
@@ -1240,14 +1271,14 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
+          <t>Mrs.Ertha gilet de flottaison 3-6 ans — 2ᵉ vichy</t>
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="C25" s="25" t="n">
-        <v>45.07</v>
+        <v>34</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>17.96</v>
       </c>
       <c r="D25" s="15">
         <f>B25*0.124</f>
@@ -1259,1072 +1290,1214 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>OU les quatre en un lot à 136 € : 71,87 € en une seule vente</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>2. À PUBLIER MAINTENANT — les pièces qui rapportent</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Bottes Forma Legacy Waterproof — 45</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="D27" s="9">
+        <f>B27*0.124</f>
+        <v/>
+      </c>
+      <c r="E27" s="10">
+        <f>B27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Boutique + Vinted + Leboncoin</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Neuves 172,49 € Dafy Moto</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>BMW Overall ProRain unisexe noir — XL</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="D28" s="15">
+        <f>B28*0.124</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>B28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Neuf 170 €</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Robe Elisabetta Franchi ivoire — 46 IT / 42 FR</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="D29" s="9">
+        <f>B29*0.124</f>
+        <v/>
+      </c>
+      <c r="E29" s="10">
+        <f>B29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Défroisser avant photos</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Jupe Sonia Rykiel midi twill cerises — 34</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C30" s="27" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="D30" s="15">
+        <f>B30*0.124</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>B30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Vérifier composition sur l'étiquette</t>
         </is>
       </c>
-      <c r="H25" s="18" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="H30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Blazer Karl Lagerfeld punto noir — 36 FR / IT 40</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B31" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C31" s="27" t="n">
         <v>25.58</v>
       </c>
-      <c r="D26" s="9">
-        <f>B26*0.124</f>
-        <v/>
-      </c>
-      <c r="E26" s="10">
-        <f>B26-D26</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="D31" s="9">
+        <f>B31*0.124</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>B31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>89 → 91 € · neuf dès 229 € Modalova — À RECONFIRMER avant publication</t>
         </is>
       </c>
-      <c r="H26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="H31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Adidas Predator Edge.1 TF — 48⅔ — 1ʳᵉ paire</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B32" s="14" t="n">
         <v>89</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C32" s="27" t="n">
         <v>56.7</v>
       </c>
-      <c r="D27" s="15">
-        <f>B27*0.124</f>
-        <v/>
-      </c>
-      <c r="E27" s="16">
-        <f>B27-D27</f>
-        <v/>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="D32" s="15">
+        <f>B32*0.124</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>B32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="H27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="H32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Adidas Predator Edge.1 TF — 48⅔ — 2ᵉ paire</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B33" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C33" s="27" t="n">
         <v>56.7</v>
       </c>
-      <c r="D28" s="9">
-        <f>B28*0.124</f>
-        <v/>
-      </c>
-      <c r="E28" s="10">
-        <f>B28-D28</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="D33" s="9">
+        <f>B33*0.124</f>
+        <v/>
+      </c>
+      <c r="E33" s="10">
+        <f>B33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Une annonce par paire</t>
         </is>
       </c>
-      <c r="H28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="H33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Robe Sandro Noaim blanche — 40</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B34" s="14" t="n">
         <v>89</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C34" s="27" t="n">
         <v>36.46</v>
       </c>
-      <c r="D29" s="15">
-        <f>B29*0.124</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>B29-D29</f>
-        <v/>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="D34" s="15">
+        <f>B34*0.124</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>B34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Retirer de Vinted d'abord</t>
         </is>
       </c>
-      <c r="H29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="H34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Plein Sport montante blanc / violet — 40</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B35" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C35" s="8" t="n">
         <v>23.34</v>
       </c>
-      <c r="D30" s="9">
-        <f>B30*0.124</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>B30-D30</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="D35" s="9">
+        <f>B35*0.124</f>
+        <v/>
+      </c>
+      <c r="E35" s="10">
+        <f>B35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>89 → 95 € · marché ~100 € Stylight, VÉRIFIER avant de publier</t>
         </is>
       </c>
-      <c r="H30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="H35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Ballerines Hogan 186 Zeppa Fashion — 36</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B36" s="14" t="n">
         <v>79</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C36" s="27" t="n">
         <v>53.05</v>
       </c>
-      <c r="D31" s="15">
-        <f>B31*0.124</f>
-        <v/>
-      </c>
-      <c r="E31" s="16">
-        <f>B31-D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="D36" s="15">
+        <f>B36*0.124</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>B36-D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Nettoyées : « aucune trace visible », PAS « neuves »</t>
         </is>
       </c>
-      <c r="H31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="H36" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Baskets adidas by Stella McCartney UB21 — 36</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B37" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C37" s="27" t="n">
         <v>27.85</v>
       </c>
-      <c r="D32" s="9">
-        <f>B32*0.124</f>
-        <v/>
-      </c>
-      <c r="E32" s="10">
-        <f>B32-D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="D37" s="9">
+        <f>B37*0.124</f>
+        <v/>
+      </c>
+      <c r="E37" s="10">
+        <f>B37-D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Neuf 94 € eBay.de</t>
         </is>
       </c>
-      <c r="H32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="H37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Robe bustier Chiara Ferragni noire — M</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B38" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C38" s="27" t="n">
         <v>25.09</v>
       </c>
-      <c r="D33" s="15">
-        <f>B33*0.124</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>B33-D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="D38" s="15">
+        <f>B38*0.124</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>B38-D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr"/>
-      <c r="H33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr"/>
+      <c r="H38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Robe Pier Antonio Gaspari bleu marine — 42</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B39" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C39" s="27" t="n">
         <v>25.46</v>
       </c>
-      <c r="D34" s="9">
-        <f>B34*0.124</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>B34-D34</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="D39" s="9">
+        <f>B39*0.124</f>
+        <v/>
+      </c>
+      <c r="E39" s="10">
+        <f>B39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>59 → 62 € · orthographe : Pier ANTONIO</t>
         </is>
       </c>
-      <c r="H34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="H39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Ballerines Massimo Dutti cuir rouge — 40 IT</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B40" s="14" t="n">
         <v>61</v>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C40" s="27" t="n">
         <v>25.87</v>
       </c>
-      <c r="D35" s="15">
-        <f>B35*0.124</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>B35-D35</f>
-        <v/>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="D40" s="15">
+        <f>B40*0.124</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>B40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G40" s="17" t="inlineStr">
         <is>
           <t>59 → 61 € · marché 70 € · pas Vinted : article neuf</t>
         </is>
       </c>
-      <c r="H35" s="18" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="H40" s="18" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Toupies Beyblade Hasbro — LOT de 4, lot n°159</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B41" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C41" s="27" t="n">
         <v>26.64</v>
       </c>
-      <c r="D36" s="9">
-        <f>B36*0.124</f>
-        <v/>
-      </c>
-      <c r="E36" s="10">
-        <f>B36-D36</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="D41" s="9">
+        <f>B41*0.124</f>
+        <v/>
+      </c>
+      <c r="E41" s="10">
+        <f>B41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>49 → 55 € · CONFIRMER le prix des 4 toupies sur leDénicheur</t>
         </is>
       </c>
-      <c r="H36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="H41" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Baskets Geox gris / argent — 35</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B42" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C42" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="D37" s="15">
-        <f>B37*0.124</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>B37-D37</f>
-        <v/>
-      </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="D42" s="15">
+        <f>B42*0.124</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>B42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>49 → 54 € · marché 55 €, plafond atteint</t>
         </is>
       </c>
-      <c r="H37" s="18" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="H42" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Morgan — jean bleu clair T.40</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B43" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C43" s="8" t="n">
         <v>7.98</v>
       </c>
-      <c r="D38" s="9">
-        <f>B38*0.124</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>B38-D38</f>
-        <v/>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="D43" s="9">
+        <f>B43*0.124</f>
+        <v/>
+      </c>
+      <c r="E43" s="10">
+        <f>B43-D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>À l'unité : 25 € par vente impossible</t>
         </is>
       </c>
-      <c r="H38" s="12" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="H43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>Morgan — jupe marron</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B44" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C44" s="8" t="n">
         <v>7.98</v>
       </c>
-      <c r="D39" s="15">
-        <f>B39*0.124</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>B39-D39</f>
-        <v/>
-      </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="D44" s="15">
+        <f>B44*0.124</f>
+        <v/>
+      </c>
+      <c r="E44" s="16">
+        <f>B44-D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr"/>
-      <c r="H39" s="18" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr"/>
+      <c r="H44" s="18" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Morgan — pantalon blanc T.40</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B45" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C45" s="8" t="n">
         <v>4.47</v>
       </c>
-      <c r="D40" s="9">
-        <f>B40*0.124</f>
-        <v/>
-      </c>
-      <c r="E40" s="10">
-        <f>B40-D40</f>
-        <v/>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="D45" s="9">
+        <f>B45*0.124</f>
+        <v/>
+      </c>
+      <c r="E45" s="10">
+        <f>B45-D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr"/>
-      <c r="H40" s="12" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Morgan — polo rouge à écusson doré L</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
+      <c r="B46" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C46" s="8" t="n">
         <v>4.47</v>
       </c>
-      <c r="D41" s="15">
-        <f>B41*0.124</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>B41-D41</f>
-        <v/>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="D46" s="15">
+        <f>B46*0.124</f>
+        <v/>
+      </c>
+      <c r="E46" s="16">
+        <f>B46-D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr"/>
-      <c r="H41" s="18" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr"/>
+      <c r="H46" s="18" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Morgan — top camel lurex L</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B47" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C47" s="8" t="n">
         <v>4.47</v>
       </c>
-      <c r="D42" s="9">
-        <f>B42*0.124</f>
-        <v/>
-      </c>
-      <c r="E42" s="10">
-        <f>B42-D42</f>
-        <v/>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="D47" s="9">
+        <f>B47*0.124</f>
+        <v/>
+      </c>
+      <c r="E47" s="10">
+        <f>B47-D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>OU les six en un lot à 98 € : 33,85 € en une seule vente</t>
         </is>
       </c>
-      <c r="H42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="H47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Morgan — polo blanc L</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B48" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C48" s="8" t="n">
         <v>4.47</v>
       </c>
-      <c r="D43" s="15">
-        <f>B43*0.124</f>
-        <v/>
-      </c>
-      <c r="E43" s="16">
-        <f>B43-D43</f>
-        <v/>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="D48" s="15">
+        <f>B48*0.124</f>
+        <v/>
+      </c>
+      <c r="E48" s="16">
+        <f>B48-D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr"/>
-      <c r="H43" s="18" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr"/>
+      <c r="H48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Robby VP550W pompe immergée — ligne 84, occasion</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
+      <c r="B49" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C49" s="8" t="n">
         <v>3.52</v>
       </c>
-      <c r="D44" s="9">
-        <f>B44*0.124</f>
-        <v/>
-      </c>
-      <c r="E44" s="10">
-        <f>B44-D44</f>
-        <v/>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="D49" s="9">
+        <f>B49*0.124</f>
+        <v/>
+      </c>
+      <c r="E49" s="10">
+        <f>B49-D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Neuve 54,90 € : plafonné · tester avant de publier</t>
         </is>
       </c>
-      <c r="H44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="H49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>Robby VP550W pompe immergée — ligne 122, SOCLE CASSÉ</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B50" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C50" s="8" t="n">
         <v>2.37</v>
       </c>
-      <c r="D45" s="15">
-        <f>B45*0.124</f>
-        <v/>
-      </c>
-      <c r="E45" s="16">
-        <f>B45-D45</f>
-        <v/>
-      </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="D50" s="15">
+        <f>B50*0.124</f>
+        <v/>
+      </c>
+      <c r="E50" s="16">
+        <f>B50-D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="G50" s="17" t="inlineStr">
         <is>
           <t>DÉFAUT À DÉCLARER + photo du socle · JAMAIS d'expédition</t>
         </is>
       </c>
-      <c r="H45" s="18" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="H50" s="18" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Toupies Beyblade Hasbro — LOT de 4, lot n°299</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
+      <c r="B51" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C51" s="8" t="n">
         <v>7.47</v>
       </c>
-      <c r="D46" s="9">
-        <f>B46*0.124</f>
-        <v/>
-      </c>
-      <c r="E46" s="10">
-        <f>B46-D46</f>
-        <v/>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="D51" s="9">
+        <f>B51*0.124</f>
+        <v/>
+      </c>
+      <c r="E51" s="10">
+        <f>B51-D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Payé 40,71 € au lieu de 21,54 € : le lot jumeau plafonne la marge</t>
         </is>
       </c>
-      <c r="H46" s="12" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="H51" s="12" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>3. LIQUIDER — vendre pour récupérer la trésorerie, pas pour la marge</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="B52" s="29" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="29" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="29" t="n"/>
+      <c r="G52" s="29" t="n"/>
+      <c r="H52" s="29" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>New Balance GS 1906 Alkaline Green — 38½</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="B53" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C53" s="8" t="n">
         <v>8.76</v>
       </c>
-      <c r="D48" s="9">
-        <f>B48*0.124</f>
-        <v/>
-      </c>
-      <c r="E48" s="10">
-        <f>B48-D48</f>
-        <v/>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="D53" s="9">
+        <f>B53*0.124</f>
+        <v/>
+      </c>
+      <c r="E53" s="10">
+        <f>B53-D53</f>
+        <v/>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>AU-DESSUS du marché 87 € StockX — à trancher</t>
         </is>
       </c>
-      <c r="H48" s="12" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="H53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande — 36</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n">
+      <c r="B54" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C54" s="8" t="n">
         <v>6.96</v>
       </c>
-      <c r="D49" s="15">
-        <f>B49*0.124</f>
-        <v/>
-      </c>
-      <c r="E49" s="16">
-        <f>B49-D49</f>
-        <v/>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="D54" s="15">
+        <f>B54*0.124</f>
+        <v/>
+      </c>
+      <c r="E54" s="16">
+        <f>B54-D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
+      <c r="G54" s="17" t="inlineStr">
         <is>
           <t>AU-DESSUS du marché 62 € eBay — à trancher</t>
         </is>
       </c>
-      <c r="H49" s="18" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="H54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Tommy Jeans baskets basses noir / blanc — 40</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
+      <c r="B55" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C55" s="8" t="n">
         <v>2.17</v>
       </c>
-      <c r="D50" s="9">
-        <f>B50*0.124</f>
-        <v/>
-      </c>
-      <c r="E50" s="10">
-        <f>B50-D50</f>
-        <v/>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="D55" s="9">
+        <f>B55*0.124</f>
+        <v/>
+      </c>
+      <c r="E55" s="10">
+        <f>B55-D55</f>
+        <v/>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>AU-DESSUS du marché 60 € Stylight — à trancher</t>
         </is>
       </c>
-      <c r="H50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="H55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante — 44</t>
         </is>
       </c>
-      <c r="B51" s="14" t="n">
+      <c r="B56" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C56" s="8" t="n">
         <v>3.45</v>
       </c>
-      <c r="D51" s="15">
-        <f>B51*0.124</f>
-        <v/>
-      </c>
-      <c r="E51" s="16">
-        <f>B51-D51</f>
-        <v/>
-      </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="D56" s="15">
+        <f>B56*0.124</f>
+        <v/>
+      </c>
+      <c r="E56" s="16">
+        <f>B56-D56</f>
+        <v/>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="G51" s="17" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>AU-DESSUS du marché 61 € idealo — à trancher</t>
         </is>
       </c>
-      <c r="H51" s="18" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="H56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>New Balance BB80 blanc / marine — 38</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B57" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C57" s="8" t="n">
         <v>6.6</v>
       </c>
-      <c r="D52" s="9">
-        <f>B52*0.124</f>
-        <v/>
-      </c>
-      <c r="E52" s="10">
-        <f>B52-D52</f>
-        <v/>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="D57" s="9">
+        <f>B57*0.124</f>
+        <v/>
+      </c>
+      <c r="E57" s="10">
+        <f>B57-D57</f>
+        <v/>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Marché 54,99 € idealo : plafond atteint</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="H57" s="12" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>5. POKÉMON — import du Japon, marges minces</t>
         </is>
       </c>
-      <c r="B53" s="27" t="n"/>
-      <c r="C53" s="27" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="29" t="n"/>
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="29" t="n"/>
+      <c r="H58" s="29" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Boosters Nihil Zero M3 — LOT de 15, n°1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B59" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="C54" s="8" t="n">
+      <c r="C59" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D54" s="9">
-        <f>B54*0.124</f>
-        <v/>
-      </c>
-      <c r="E54" s="10">
-        <f>B54-D54</f>
-        <v/>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="D59" s="9">
+        <f>B59*0.124</f>
+        <v/>
+      </c>
+      <c r="E59" s="10">
+        <f>B59-D59</f>
+        <v/>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>PHOTOGRAPHIER LE BLISTER SCELLÉ avant d'ouvrir la box</t>
         </is>
       </c>
-      <c r="H54" s="12" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="H59" s="12" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Boosters Nihil Zero M3 — LOT de 15, n°2</t>
         </is>
       </c>
-      <c r="B55" s="14" t="n">
+      <c r="B60" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C60" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D55" s="15">
-        <f>B55*0.124</f>
-        <v/>
-      </c>
-      <c r="E55" s="16">
-        <f>B55-D55</f>
-        <v/>
-      </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="D60" s="15">
+        <f>B60*0.124</f>
+        <v/>
+      </c>
+      <c r="E60" s="16">
+        <f>B60-D60</f>
+        <v/>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
         <is>
           <t>« Boosters non pesés, non triés » dans l'annonce</t>
         </is>
       </c>
-      <c r="H55" s="18" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="H60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Boosters MEGA Storm Emeralda M6 — LOT de 2</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B61" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C61" s="8" t="n">
         <v>3.9</v>
       </c>
-      <c r="D56" s="9">
-        <f>B56*0.124</f>
-        <v/>
-      </c>
-      <c r="E56" s="10">
-        <f>B56-D56</f>
-        <v/>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="D61" s="9">
+        <f>B61*0.124</f>
+        <v/>
+      </c>
+      <c r="E61" s="10">
+        <f>B61-D61</f>
+        <v/>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Set sorti le 31/07/2026, forte demande</t>
         </is>
       </c>
-      <c r="H56" s="12" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
+      <c r="H61" s="12" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>4. PLUS TARD — ne pas publier maintenant</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n"/>
-      <c r="C57" s="29" t="n"/>
-      <c r="D57" s="29" t="n"/>
-      <c r="E57" s="29" t="n"/>
-      <c r="F57" s="29" t="n"/>
-      <c r="G57" s="29" t="n"/>
-      <c r="H57" s="29" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B62" s="31" t="n"/>
+      <c r="C62" s="31" t="n"/>
+      <c r="D62" s="31" t="n"/>
+      <c r="E62" s="31" t="n"/>
+      <c r="F62" s="31" t="n"/>
+      <c r="G62" s="31" t="n"/>
+      <c r="H62" s="31" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Lot 20 sandales et tongs — EN LOT</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B63" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C58" s="25" t="n">
+      <c r="C63" s="27" t="n">
         <v>115.25</v>
       </c>
-      <c r="D58" s="9">
-        <f>B58*0.124</f>
-        <v/>
-      </c>
-      <c r="E58" s="10">
-        <f>B58-D58</f>
-        <v/>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="D63" s="9">
+        <f>B63*0.124</f>
+        <v/>
+      </c>
+      <c r="E63" s="10">
+        <f>B63-D63</f>
+        <v/>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>FÉVRIER-MARS, quand le revendeur prépare l'été</t>
         </is>
       </c>
-      <c r="H58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="H63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower — 38</t>
         </is>
       </c>
-      <c r="B59" s="14" t="n">
+      <c r="B64" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="C59" s="25" t="n">
+      <c r="C64" s="27" t="n">
         <v>26.61</v>
       </c>
-      <c r="D59" s="15">
-        <f>B59*0.124</f>
-        <v/>
-      </c>
-      <c r="E59" s="16">
-        <f>B59-D59</f>
-        <v/>
-      </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="D64" s="15">
+        <f>B64*0.124</f>
+        <v/>
+      </c>
+      <c r="E64" s="16">
+        <f>B64-D64</f>
+        <v/>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
         <is>
           <t>Neuve 140 € wehaveit.fr · prix valable SI l'authentification passe</t>
         </is>
       </c>
-      <c r="H59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="H64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>TOTAL — 48 annonces chiffrées</t>
         </is>
       </c>
-      <c r="B60" s="31">
-        <f>B6+B7+B8+B9+B10+B12+B13+B15+B16+B17+B18+B19+B20+B22+B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B48+B49+B50+B51+B52+B54+B55+B56+B58+B59</f>
-        <v/>
-      </c>
-      <c r="C60" s="31">
-        <f>C6+C7+C8+C9+C10+C12+C13+C15+C16+C17+C18+C19+C20+C22+C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C48+C49+C50+C51+C52+C54+C55+C56+C58+C59</f>
-        <v/>
-      </c>
-      <c r="D60" s="32">
-        <f>B60*0.124</f>
-        <v/>
-      </c>
-      <c r="E60" s="31">
-        <f>B60-D60</f>
-        <v/>
-      </c>
-      <c r="F60" s="33" t="n"/>
-      <c r="G60" s="33" t="n"/>
-      <c r="H60" s="33" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B65" s="33">
+        <f>B6+B7+B8+B9+B10+B11+B12+B20+B21+B22+B23+B24+B25+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48+B49+B50+B51+B53+B54+B55+B56+B57+B59+B60+B61+B63+B64</f>
+        <v/>
+      </c>
+      <c r="C65" s="33">
+        <f>C6+C7+C8+C9+C10+C11+C12+C20+C21+C22+C23+C24+C25+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48+C49+C50+C51+C53+C54+C55+C56+C57+C59+C60+C61+C63+C64</f>
+        <v/>
+      </c>
+      <c r="D65" s="34">
+        <f>B65*0.124</f>
+        <v/>
+      </c>
+      <c r="E65" s="33">
+        <f>B65-D65</f>
+        <v/>
+      </c>
+      <c r="F65" s="35" t="n"/>
+      <c r="G65" s="35" t="n"/>
+      <c r="H65" s="35" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>MARGE / VENTE en vert : l'objectif de 25 € par vente est atteint. En rouge : le prix de rue plafonne, il ne peut pas l'être.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Règle : ces prix sont calés SOUS le moins cher trouvé sur Internet. Quatre lignes en « Liquider » sont au-dessus — décision à prendre.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -655,7 +655,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>✅ VENDU — 343 € encaissés de clients réels</t>
+          <t>✅ VENDU — 353 € encaissés de clients réels</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7.47</v>
+        <v>16.23</v>
       </c>
       <c r="D10" s="9">
         <f>B10*0.124</f>
@@ -821,7 +821,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Encaissé le 09/08</t>
+          <t>Encaissé le 09/08 · corrigé 40 → 50 €</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -655,7 +655,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>✅ VENDU — 353 € encaissés de clients réels</t>
+          <t>✅ VENDU — 373 € encaissés de clients réels</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2.49</v>
+        <v>20.01</v>
       </c>
       <c r="D6" s="9">
         <f>B6*0.124</f>
@@ -693,7 +693,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Encaissé le 09/08 · marge +2,49 € seulement</t>
+          <t>Encaissé le 09/08 · corrigé 135 → 155 €</t>
         </is>
       </c>
       <c r="H6" s="12" t="n"/>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -655,7 +655,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>✅ VENDU — 373 € encaissés de clients réels</t>
+          <t>✅ VENDU — 473 € encaissés de clients réels</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Vendue le 12/08 · EXPÉDIÉE le 14/08, locker Mondial Relay · en attente d'encaissement</t>
+          <t>Vendue le 12/08 · EXPÉDIÉE le 14/08, locker Mondial Relay · ENCAISSÉE le 23/08</t>
         </is>
       </c>
       <c r="H7" s="18" t="n"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Expédiée le 03/08 · encaissée le 10/08 · trop bas, passer à 18 €</t>
+          <t>Expédiée le 03/08 · encaissée le 10/08 · trop bas, passer à 16 €</t>
         </is>
       </c>
       <c r="H11" s="18" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Encaissée le 10/08 · trop bas, passer à 18 €</t>
+          <t>Encaissée le 10/08 · trop bas, passer à 16 €</t>
         </is>
       </c>
       <c r="H12" s="12" t="n"/>
@@ -1021,7 +1021,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Booster Pokémon High Class MEGA Dream ex M2a</t>
+          <t>Vidéoprojecteur PHILIPS NeoPix 110 — très bon état, testé</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Gardé le 13/08</t>
+          <t>Gardé le 23/08</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>Coût 12,95 € · invendable avec profit : marché à 12,99 €</t>
+          <t>Coût 50,40 € · facture FB2026-49549 · aucune recette, aucune URSSAF · sortie au registre des objets mobiliers</t>
         </is>
       </c>
       <c r="H17" s="18" t="n"/>
@@ -1059,7 +1059,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>— TOTAL PRÉLEVÉ : 150,50 €, remboursé au compte pro en apport</t>
+          <t>— TOTAL PRÉLEVÉ : 187,95 €, remboursé au compte pro en apport</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>4.99</v>
+        <v>3.25</v>
       </c>
       <c r="D20" s="9">
         <f>B20*0.124</f>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Moins cher du net 15 €/paire · 25 € par vente HORS D'ATTEINTE</t>
+          <t>PRIX REVU le 16/08 (18 → 16 €) · moins cher du net 15-16 € · 25 € par vente HORS D'ATTEINTE</t>
         </is>
       </c>
       <c r="H20" s="12" t="n"/>
@@ -2285,14 +2285,14 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Boosters Nihil Zero M3 — LOT de 15, n°1</t>
+          <t>Display Pokémon Nihil Zero M3 — box scellée entière, 30 boosters</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="D59" s="9">
         <f>B59*0.124</f>
@@ -2304,46 +2304,24 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Compte professionnel — Leboncoin</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>PHOTOGRAPHIER LE BLISTER SCELLÉ avant d'ouvrir la box</t>
+          <t>Vendue scellée, pas en lots — SCELLÉ = preuve non pesé/trié, photo du blister avant envoi</t>
         </is>
       </c>
       <c r="H59" s="12" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>Boosters Nihil Zero M3 — LOT de 15, n°2</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="D60" s="15">
-        <f>B60*0.124</f>
-        <v/>
-      </c>
-      <c r="E60" s="16">
-        <f>B60-D60</f>
-        <v/>
-      </c>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>Leboncoin, main propre</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>« Boosters non pesés, non triés » dans l'annonce</t>
-        </is>
-      </c>
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="15" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="17" t="n"/>
       <c r="H60" s="18" t="n"/>
     </row>
     <row r="61">
@@ -2368,7 +2346,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Compte professionnel — Leboncoin</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -2457,47 +2435,99 @@
       <c r="H64" s="18" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL — 48 annonces chiffrées</t>
-        </is>
-      </c>
-      <c r="B65" s="33">
-        <f>B6+B7+B8+B9+B10+B11+B12+B20+B21+B22+B23+B24+B25+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48+B49+B50+B51+B53+B54+B55+B56+B57+B59+B60+B61+B63+B64</f>
-        <v/>
-      </c>
-      <c r="C65" s="33">
-        <f>C6+C7+C8+C9+C10+C11+C12+C20+C21+C22+C23+C24+C25+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48+C49+C50+C51+C53+C54+C55+C56+C57+C59+C60+C61+C63+C64</f>
-        <v/>
-      </c>
-      <c r="D65" s="34">
-        <f>B65*0.124</f>
-        <v/>
-      </c>
-      <c r="E65" s="33">
-        <f>B65-D65</f>
-        <v/>
-      </c>
-      <c r="F65" s="35" t="n"/>
-      <c r="G65" s="35" t="n"/>
-      <c r="H65" s="35" t="n"/>
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>6. INFORMATIQUE — hors périmètre mode, pas encore tarifé</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n"/>
+      <c r="C65" s="31" t="n"/>
+      <c r="D65" s="31" t="n"/>
+      <c r="E65" s="31" t="n"/>
+      <c r="F65" s="31" t="n"/>
+      <c r="G65" s="31" t="n"/>
+      <c r="H65" s="31" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Unité centrale gaming Acer Predator G3-605 — i7-4790, GTX 980, 16 Go RAM</t>
+        </is>
+      </c>
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t>à tarifer</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Leboncoin informatique / eBay — pas la boutique</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Coût 88,20 € · facture FB2026-49549 · relever le marché avant de fixer un prix</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>MARGE / VENTE en vert : l'objectif de 25 € par vente est atteint. En rouge : le prix de rue plafonne, il ne peut pas l'être.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Règle : ces prix sont calés SOUS le moins cher trouvé sur Internet. Quatre lignes en « Liquider » sont au-dessus — décision à prendre.</t>
-        </is>
-      </c>
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL — 47 annonces chiffrées</t>
+        </is>
+      </c>
+      <c r="B67" s="33">
+        <f>B6+B7+B8+B9+B10+B11+B12+B20+B21+B22+B23+B24+B25+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48+B49+B50+B51+B53+B54+B55+B56+B57+B59+B61+B63+B64</f>
+        <v/>
+      </c>
+      <c r="C67" s="33">
+        <f>C6+C7+C8+C9+C10+C11+C12+C20+C21+C22+C23+C24+C25+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48+C49+C50+C51+C53+C54+C55+C56+C57+C59+C61+C63+C64</f>
+        <v/>
+      </c>
+      <c r="D67" s="34">
+        <f>B67*0.124</f>
+        <v/>
+      </c>
+      <c r="E67" s="33">
+        <f>B67-D67</f>
+        <v/>
+      </c>
+      <c r="F67" s="35" t="n"/>
+      <c r="G67" s="35" t="n"/>
+      <c r="H67" s="35" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>MARGE / VENTE en vert : l'objectif de 25 € par vente est atteint. En rouge : le prix de rue plafonne, il ne peut pas l'être.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Règle : ces prix sont calés SOUS le moins cher trouvé sur Internet. Quatre lignes en « Liquider » sont au-dessus — décision à prendre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP, calculé sur le prix de vente encaissé. À mettre de côté à chaque vente, pas à la fin du trimestre.</t>
         </is>

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -2437,7 +2437,7 @@
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>6. INFORMATIQUE — hors périmètre mode, pas encore tarifé</t>
+          <t>6. INFORMATIQUE — hors périmètre mode</t>
         </is>
       </c>
       <c r="B65" s="31" t="n"/>
@@ -2454,34 +2454,28 @@
           <t>Unité centrale gaming Acer Predator G3-605 — i7-4790, GTX 980, 16 Go RAM</t>
         </is>
       </c>
-      <c r="B66" s="21" t="inlineStr">
-        <is>
-          <t>à tarifer</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B66" s="21" t="n">
+        <v>190</v>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="D66" s="21">
+        <f>B66*0.124</f>
+        <v/>
+      </c>
+      <c r="E66" s="21">
+        <f>B66-D66</f>
+        <v/>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Leboncoin informatique / eBay — pas la boutique</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>Coût 88,20 € · facture FB2026-49549 · relever le marché avant de fixer un prix</t>
+          <t>Coût 88,20 € · marge réelle 55,09 € après commission eBay (12 % + 0,35 €) et URSSAF — pas 78,24 €, qui serait la marge sans commission</t>
         </is>
       </c>
       <c r="H66" s="12" t="n"/>
@@ -2489,15 +2483,15 @@
     <row r="67">
       <c r="A67" s="32" t="inlineStr">
         <is>
-          <t>TOTAL — 47 annonces chiffrées</t>
+          <t>TOTAL — 48 annonces chiffrées</t>
         </is>
       </c>
       <c r="B67" s="33">
-        <f>B6+B7+B8+B9+B10+B11+B12+B20+B21+B22+B23+B24+B25+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48+B49+B50+B51+B53+B54+B55+B56+B57+B59+B61+B63+B64</f>
+        <f>B6+B7+B8+B9+B10+B11+B12+B20+B21+B22+B23+B24+B25+B27+B28+B29+B30+B31+B32+B33+B34+B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48+B49+B50+B51+B53+B54+B55+B56+B57+B59+B61+B63+B64+B66</f>
         <v/>
       </c>
       <c r="C67" s="33">
-        <f>C6+C7+C8+C9+C10+C11+C12+C20+C21+C22+C23+C24+C25+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48+C49+C50+C51+C53+C54+C55+C56+C57+C59+C61+C63+C64</f>
+        <f>C6+C7+C8+C9+C10+C11+C12+C20+C21+C22+C23+C24+C25+C27+C28+C29+C30+C31+C32+C33+C34+C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48+C49+C50+C51+C53+C54+C55+C56+C57+C59+C61+C63+C64+C66</f>
         <v/>
       </c>
       <c r="D67" s="34">

--- a/exports/maison-nsaia-liste-de-vente.xlsx
+++ b/exports/maison-nsaia-liste-de-vente.xlsx
@@ -1019,47 +1019,19 @@
       <c r="H16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Vidéoprojecteur PHILIPS NeoPix 110 — très bon état, testé</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Gardé le 23/08</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>Coût 50,40 € · facture FB2026-49549 · aucune recette, aucune URSSAF · sortie au registre des objets mobiliers</t>
-        </is>
-      </c>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="17" t="n"/>
       <c r="H17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>— TOTAL PRÉLEVÉ : 187,95 €, remboursé au compte pro en apport</t>
+          <t>— TOTAL PRÉLEVÉ : 137,55 €, remboursé au compte pro en apport</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
@@ -1089,7 +1061,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>NE PAS DÉCLARER À L'URSSAF · un micro-entrepreneur ne se vend pas à lui-même</t>
+          <t>NE PAS DÉCLARER À L'URSSAF · un micro-entrepreneur ne se vend pas à lui-même · Le vidéoprojecteur Philips NeoPix 110 n'apparaît plus ici : réglé avec l'argent personnel du porteur du projet, jamais un achat professionnel.</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
